--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>787986899</t>
+          <t>787989467</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>abeltacillo99</t>
+          <t>Regulo02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-10-09 01:31:03</t>
+          <t>2025-10-10 00:05:05</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>787987004</t>
+          <t>787989506</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>angelito1725b</t>
+          <t>alfajorcito</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-10-09 04:42:30</t>
+          <t>2025-10-10 02:22:02</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>787987112</t>
+          <t>787989509</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morales26</t>
+          <t>kathyta22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-10-09 05:45:11</t>
+          <t>2025-10-10 02:30:04</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>787987523</t>
+          <t>787989977</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reyna</t>
+          <t>Jcarlos40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-10-09 07:57:08</t>
+          <t>2025-10-10 07:17:12</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>787987604</t>
+          <t>787990124</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>luisaliaga</t>
+          <t>Ryukzaki</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/50.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-09 08:19:47</t>
+          <t>2025-10-10 07:59:58</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>787987619</t>
+          <t>787990217</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jose1912</t>
+          <t>nadiadm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-10-09 08:23:44</t>
+          <t>2025-10-10 08:31:41</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>787987667</t>
+          <t>787990247</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teodora1234</t>
+          <t>josue1412</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/40.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-10-09 08:35:02</t>
+          <t>2025-10-10 08:45:04</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>787987733</t>
+          <t>787990391</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nandololi</t>
+          <t>lizie</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-10-09 08:51:10</t>
+          <t>2025-10-10 09:16:51</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>787987844</t>
+          <t>787990466</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cilos12</t>
+          <t>marchena</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-09 09:21:43</t>
+          <t>2025-10-10 09:33:20</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>787987973</t>
+          <t>787990553</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SoyBryan123</t>
+          <t>Jerson07.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-10-09 09:59:12</t>
+          <t>2025-10-10 09:49:20</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>787987994</t>
+          <t>787990808</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hernaldi</t>
+          <t>franco25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-09 10:02:29</t>
+          <t>2025-10-10 10:52:13</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>787988015</t>
+          <t>787990832</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOLASDEBALA</t>
+          <t>74625867</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-10-09 10:06:34</t>
+          <t>2025-10-10 10:59:25</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>787988102</t>
+          <t>787990991</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yanda14</t>
+          <t>73646109</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-10-09 10:37:46</t>
+          <t>2025-10-10 11:18:19</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>787988129</t>
+          <t>787991015</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ginarhcp</t>
+          <t>Gustavo2004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-10-09 10:46:34</t>
+          <t>2025-10-10 11:21:37</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>787988162</t>
+          <t>787991084</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>moises89</t>
+          <t>jaimenpintadochingue...</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-10-09 11:01:15</t>
+          <t>2025-10-10 11:30:32</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>787988168</t>
+          <t>787991114</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pedrotest</t>
+          <t>YuberVallejos07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-10-09 11:02:52</t>
+          <t>2025-10-10 11:37:41</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>787988333</t>
+          <t>787991276</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JHOE21</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-10-09 11:39:43</t>
+          <t>2025-10-10 12:16:18</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>787988438</t>
+          <t>787991291</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Elmechas89</t>
+          <t>chispafc</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S/0.26</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-09 12:14:51</t>
+          <t>2025-10-10 12:21:18</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>787988486</t>
+          <t>787991372</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>924839084</t>
+          <t>Diegoxde03</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-09 12:29:50</t>
+          <t>2025-10-10 12:39:21</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>787988579</t>
+          <t>787991477</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>chrisz10</t>
+          <t>alexander1994</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-09 12:45:14</t>
+          <t>2025-10-10 12:59:04</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>787988735</t>
+          <t>787991504</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>danielito1996</t>
+          <t>divan31</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-10-09 13:20:41</t>
+          <t>2025-10-10 13:05:13</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>787988933</t>
+          <t>787991546</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>testelo</t>
+          <t>jhoseph01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-09 14:22:30</t>
+          <t>2025-10-10 13:17:34</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>787988939</t>
+          <t>787991630</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FranzuaxD</t>
+          <t>darkman77</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-09 14:23:35</t>
+          <t>2025-10-10 13:37:33</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>787988951</t>
+          <t>787991693</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ginoxx123</t>
+          <t>Wolverinex22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-09 14:27:34</t>
+          <t>2025-10-10 14:01:03</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>787989104</t>
+          <t>787991741</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ITALOS</t>
+          <t>ulises89</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-09 16:02:47</t>
+          <t>2025-10-10 14:24:02</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>787989182</t>
+          <t>787991744</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>javicho1996</t>
+          <t>Eryan16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.90</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-10-09 17:13:15</t>
+          <t>2025-10-10 14:27:25</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>787989272</t>
+          <t>787991771</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jeancarlo2002</t>
+          <t>cordova89</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-10-09 18:35:24</t>
+          <t>2025-10-10 14:42:20</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>787989293</t>
+          <t>787991804</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ivanza84</t>
+          <t>Fadriji</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-10-09 19:04:08</t>
+          <t>2025-10-10 14:54:18</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>787989344</t>
+          <t>787991831</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lm</t>
+          <t>hcvv2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-10-09 20:32:42</t>
+          <t>2025-10-10 15:02:39</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>787989347</t>
+          <t>787991870</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rodrigogonzales</t>
+          <t>Elizagarcia</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-10-09 20:34:41</t>
+          <t>2025-10-10 15:26:18</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>787989350</t>
+          <t>787991921</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>frankomt31</t>
+          <t>popeye4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-10-09 20:34:59</t>
+          <t>2025-10-10 15:55:51</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>787989368</t>
+          <t>787991924</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Flavia03</t>
+          <t>manuelsa19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-10-09 20:59:35</t>
+          <t>2025-10-10 15:58:38</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>787989374</t>
+          <t>787992020</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bagnerlo</t>
+          <t>luisjauregui</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-10-09 21:11:24</t>
+          <t>2025-10-10 17:14:03</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>787989377</t>
+          <t>787992032</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>angelperez</t>
+          <t>Julio_Mc</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-10-09 21:22:15</t>
+          <t>2025-10-10 17:17:15</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>787989383</t>
+          <t>787992053</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Enriquejosensn</t>
+          <t>guerrerovaldivia25</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-10-09 21:29:25</t>
+          <t>2025-10-10 17:46:20</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>787989401</t>
+          <t>787992176</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eduardo1816</t>
+          <t>jair11</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-10-09 21:55:00</t>
+          <t>2025-10-10 19:45:23</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>787989416</t>
+          <t>787992185</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tifa1587</t>
+          <t>reybis</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>S/0.10</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2025-10-09 22:15:39</t>
+          <t>2025-10-10 19:50:13</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>787989419</t>
+          <t>787992197</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Edgarjose</t>
+          <t>Fredjav10</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-10-09 22:17:39</t>
+          <t>2025-10-10 20:08:39</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>787989431</t>
+          <t>787992239</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jaluva</t>
+          <t>insano</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-10-09 22:30:37</t>
+          <t>2025-10-10 20:48:15</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>787989449</t>
+          <t>787992254</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gomez2007</t>
+          <t>clik111</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-10-09 23:11:36</t>
+          <t>2025-10-10 21:26:43</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>787989461</t>
+          <t>787992257</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AtCeLlZz</t>
+          <t>yacori20</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2440,7 +2440,5527 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2025-10-09 23:43:11</t>
+          <t>2025-10-10 21:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>787992260</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>andrea1330</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-10-10 21:37:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>787992269</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Carlitosurus</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-10-10 21:41:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>787992278</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>camote30</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-10-10 21:50:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>787992281</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>silchato_345</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-10-10 21:51:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>787992284</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>paulino</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-10-10 21:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>787992296</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Zsnes11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-10-10 22:19:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>787992305</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Jhofran87</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-10-10 22:38:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>787992311</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BKNERITO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-10-10 22:48:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>787992326</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HANS222</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-10-10 23:17:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>787992350</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Alexsklant</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-10-11 00:13:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>787992356</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>RociiY</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-10-11 00:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>787992368</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>fernando5151</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-10-11 00:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>787992386</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>umbrella_28</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-10-11 01:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>787992407</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>milifabian98</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-10-11 02:42:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>787992653</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Anali16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-10-11 06:48:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>787992689</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Andresx10</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-10-11 07:09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>787993013</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ufo333</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-10-11 08:54:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>787993142</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Diamont</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-10-11 09:24:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>787993241</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>papaartu74</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-10-11 09:47:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>787993364</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>monin</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-10-11 10:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>787993484</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>victormanuel11</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.50</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-10-11 10:52:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>787993820</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Alexhamilton2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.50</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-10-11 12:12:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>787993877</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>gianfra</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-10-11 12:28:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>787994015</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>beimer</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-10-11 13:06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>787994078</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>JhaninoVB</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-10-11 13:20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>787994084</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>hugo1988</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-10-11 13:22:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>787994204</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>melvinedgardo</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-10-11 14:34:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>787994216</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>julioalvaro34</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-10-11 14:42:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>787994219</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>JCOV48</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-10-11 14:42:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>787994231</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kervin2012</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-10-11 14:47:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>787994243</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>12345calle</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-10-11 15:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>787994318</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pala123</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-10-11 15:53:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>787994357</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>percymeza</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-10-11 16:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>787994441</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ronald...</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-10-11 17:32:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>787994456</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>rocio3021</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-10-11 17:49:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>787994462</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Darwin125</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-10-11 17:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>787994471</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>greysmartinez</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-10-11 18:03:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>787994483</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>alcantarita</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.14</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-10-11 18:18:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>787994522</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>brandon30</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-10-11 18:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>787994534</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>davidsamuelroblesram...</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-10-11 19:17:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>787994621</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>yulinio03</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-10-11 21:15:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>787994639</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Jose3031</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-10-11 21:28:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>787994663</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Rafa2025</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-10-11 22:30:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>787994666</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>henrycaira73</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-10-11 22:35:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>787994669</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wadesk8</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.03</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-10-11 22:43:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>787994672</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AsMarcelo</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-10-11 22:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>787994678</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>fredy10</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-10-11 22:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>787994708</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>mayate</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-10-11 23:22:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>787995041</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>luis198838</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-10-12 06:40:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>787995263</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>oso3036</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-10-12 08:04:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>787995359</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-10-12 08:50:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>787995413</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Virgo</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-10-12 09:08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>787995527</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>jorgenassi25</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-10-12 09:41:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>787995686</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>eriqueu</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-10-12 10:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>787995779</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>guillen29</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:09:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>787995806</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Yunely1234556</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-10-12 11:20:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>787995932</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>geminis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-10-12 12:13:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>787995953</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>mat9521</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2025-10-12 12:22:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>787996025</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>mizael123</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2025-10-12 12:51:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>787996094</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Noguera</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2025-10-12 13:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>787996184</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>rodri0606</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2025-10-12 14:23:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>787996235</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>tonytony14</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2025-10-12 14:50:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>787996271</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>bangal</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2025-10-12 15:24:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>787996409</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>santosfsx</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2025-10-12 17:15:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>787996448</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>rubiocastillo</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2025-10-12 18:06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>787996454</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>alvarohuaja</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2025-10-12 18:09:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>787996457</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>inofuente66</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2025-10-12 18:14:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>787996478</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Lamota31</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2025-10-12 18:47:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>787996490</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>aliancito</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:03:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>787996502</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Gonzali99</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2025-10-12 19:18:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>787996532</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>tenorio76</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2025-10-12 20:07:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>787996541</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>gustavoadolfo31</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2025-10-12 20:33:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>787996547</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>carloscarmenlu1994</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2025-10-12 21:00:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>787996550</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>orlandoperu</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2025-10-12 21:09:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>787996571</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Robrisa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2025-10-12 21:30:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>787996577</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>LilyCL18</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2025-10-12 21:49:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>787996586</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>futbol45</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2025-10-12 22:09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>787996595</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lisbethtc</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2025-10-12 22:33:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>787996598</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Flor050185</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2025-10-12 22:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>787996604</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>JEANKRATOZ</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2025-10-12 23:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>787996610</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Joseth20</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2025-10-12 23:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>787996613</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Jorge999</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2025-10-12 23:22:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>787996616</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>parcerito</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2025-10-12 23:33:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>787996637</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>mero</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:02:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>787996646</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>conny</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>787996733</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>andresitotc</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2025-10-13 03:53:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>787996745</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Renzoo</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2025-10-13 04:04:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>787997276</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>70097810</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2025-10-13 08:31:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>787997453</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>laflorida</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>S/12.00</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2025-10-13 09:19:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>787997480</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Eistin</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2025-10-13 09:25:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>787997516</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dannermoreto</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>S/0.13</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2025-10-13 09:37:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>787997738</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>edgarvalen</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2025-10-13 10:32:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>787997837</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Jhon2003</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2025-10-13 10:57:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>787998128</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>deku274</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2025-10-13 12:27:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>787998317</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>fabriciochavez25</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2025-10-13 13:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>787998341</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>meloingrid</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2025-10-13 13:56:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>787998371</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>alanpalomino25</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2025-10-13 14:18:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>787998416</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>genezz</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2025-10-13 14:56:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>787998467</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>fatima22</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2025-10-13 15:34:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>787998506</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Jacsoncastanon</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2025-10-13 15:51:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>787998554</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>salazar123</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2025-10-13 16:19:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>787998575</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>JBON</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2025-10-13 16:26:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>787998692</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>GabrielR</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2025-10-13 18:09:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>787998713</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>enrruco12</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2025-10-13 18:46:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>787998746</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jesusgerson</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>S/179.58</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2025-10-13 19:30:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>787998758</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Fresqui</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2025-10-13 19:38:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>787998764</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>cayetano21</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2025-10-13 19:52:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>787998776</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Franciscotyt</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2025-10-13 19:56:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>787998797</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>luiseltravieso</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>S/179.53</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2025-10-13 20:15:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>787998803</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>danibito</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2025-10-13 20:23:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>787998824</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>xander2501</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2025-10-13 21:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>787998845</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>WIENNER12</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2025-10-13 21:49:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>787998857</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Tonipe</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2025-10-13 22:14:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>787998869</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>BLADES</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2025-10-13 22:30:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>787998887</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>efrita</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2025-10-13 23:18:52</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/20.00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1961,6 +1961,1446 @@
       <c r="J32" t="inlineStr">
         <is>
           <t>2025-10-14 23:31:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788001668</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>brayer1991</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788001986</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Lasro</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-10-15 06:46:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788002055</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lui</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-10-15 07:38:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788002124</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Kevinparedes21</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-10-15 08:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788002271</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lexisma</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-10-15 08:56:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788002556</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>tigre0987</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-10-15 10:06:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788002709</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dianabel</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-10-15 10:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788003142</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IsidoroXD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-10-15 12:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788003288</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>elmer.subiate</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:28:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788003375</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>julianapaz</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-10-15 14:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788003408</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>smith11</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-10-15 14:26:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788003429</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Anthony0815</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-10-15 14:41:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788003480</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jimmisaavedraguevara</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:34:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788003486</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Joseleon39</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:36:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788003513</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>pres</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:56:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788003522</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>manuel1996</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788003534</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>helenrr</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-10-15 16:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788003561</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Richard1986</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-10-15 16:22:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788003603</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>klibertev</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-10-15 16:44:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788003705</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>judith19</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-10-15 17:29:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788003729</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>betbet123</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-10-15 17:39:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788003759</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>75705801</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-10-15 18:15:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788003762</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>luisino</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-10-15 18:16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788003768</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>neni22</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-10-15 18:20:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788003846</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>maritza</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-10-15 19:54:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788003885</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tablarock</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:34:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788003912</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>leymer</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-10-15 21:12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788003933</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fang47</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:41:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788003954</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Jairpaifa</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-10-15 23:05:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788003960</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>victor1677</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-10-15 23:21:09</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>787998911</t>
+          <t>788006528</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ember12</t>
+          <t>Sheyla2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-10-14 00:41:47</t>
+          <t>2025-10-17 01:07:05</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>787998920</t>
+          <t>788006564</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gocha0813</t>
+          <t>nickydesign</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-10-14 01:45:13</t>
+          <t>2025-10-17 02:57:14</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>787998938</t>
+          <t>788006594</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>marco777</t>
+          <t>Lucky72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-10-14 02:24:49</t>
+          <t>2025-10-17 03:20:08</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>787999001</t>
+          <t>788006600</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lusito</t>
+          <t>samiloki</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-10-14 03:53:56</t>
+          <t>2025-10-17 03:22:10</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>787999238</t>
+          <t>788006663</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wacoo</t>
+          <t>Giovani94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-14 06:55:33</t>
+          <t>2025-10-17 04:36:36</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>787999391</t>
+          <t>788006762</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xivi88</t>
+          <t>marco2004</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S/0.07</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-10-14 07:51:16</t>
+          <t>2025-10-17 05:44:48</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>787999697</t>
+          <t>788006777</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wilmer26</t>
+          <t>xbjeta15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-10-14 09:13:56</t>
+          <t>2025-10-17 05:50:06</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>787999748</t>
+          <t>788007080</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>leidymilagros</t>
+          <t>Anderson.corrales</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-10-14 09:24:24</t>
+          <t>2025-10-17 07:55:42</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>787999850</t>
+          <t>788007218</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JOSEJAVIER19</t>
+          <t>Pieer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-14 09:49:47</t>
+          <t>2025-10-17 08:16:32</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788000033</t>
+          <t>788007260</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JimmyNC10</t>
+          <t>valderaajes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.67</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-10-14 10:32:05</t>
+          <t>2025-10-17 08:34:15</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788000087</t>
+          <t>788007446</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Libra2510</t>
+          <t>misho</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S/0.04</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-14 10:44:10</t>
+          <t>2025-10-17 09:26:58</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788000330</t>
+          <t>788007623</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>marzocemt</t>
+          <t>huauya_01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-10-14 11:11:22</t>
+          <t>2025-10-17 10:14:40</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788000471</t>
+          <t>788007728</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lujanpalacios</t>
+          <t>wilsonsinsero</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-10-14 11:38:26</t>
+          <t>2025-10-17 10:36:02</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788000798</t>
+          <t>788007953</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TESTVENTAS</t>
+          <t>Nelson.vargas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S/50.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-10-14 12:42:00</t>
+          <t>2025-10-17 11:15:16</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788001038</t>
+          <t>788008232</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denis2013</t>
+          <t>santoyo123</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-10-14 14:18:03</t>
+          <t>2025-10-17 12:12:53</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788001044</t>
+          <t>788008307</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>oscarsanchez</t>
+          <t>WILMER1985</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-10-14 14:26:18</t>
+          <t>2025-10-17 12:28:31</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788001083</t>
+          <t>788008346</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anto3333</t>
+          <t>ricardoic</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-10-14 14:56:48</t>
+          <t>2025-10-17 12:35:03</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788001176</t>
+          <t>788008607</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rubig</t>
+          <t>raymaracierta23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-14 15:55:48</t>
+          <t>2025-10-17 13:42:55</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788001194</t>
+          <t>788008649</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>telo666</t>
+          <t>osmar17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-14 16:00:25</t>
+          <t>2025-10-17 13:56:18</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788001278</t>
+          <t>788008685</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RoiAR</t>
+          <t>rosimao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-14 16:52:52</t>
+          <t>2025-10-17 14:22:25</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788001332</t>
+          <t>788008721</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Calerithoxtlpv</t>
+          <t>lizeth12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-10-14 17:27:33</t>
+          <t>2025-10-17 15:06:34</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788001401</t>
+          <t>788008754</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>huarcaya.rey</t>
+          <t>Alx1996</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-14 17:55:57</t>
+          <t>2025-10-17 15:30:01</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788001413</t>
+          <t>788008784</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jossuerelax</t>
+          <t>Marx010506</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-14 18:06:11</t>
+          <t>2025-10-17 15:47:14</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788001458</t>
+          <t>788008898</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Junior26</t>
+          <t>maxlandii</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-14 18:58:21</t>
+          <t>2025-10-17 17:19:14</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788001491</t>
+          <t>788008910</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rufino123</t>
+          <t>Oscar20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-14 19:23:30</t>
+          <t>2025-10-17 17:30:14</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788001575</t>
+          <t>788009045</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>milanesa</t>
+          <t>Duran15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-10-14 21:02:30</t>
+          <t>2025-10-17 19:18:01</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788001587</t>
+          <t>788009087</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jerson23</t>
+          <t>Robert241981</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-10-14 21:11:58</t>
+          <t>2025-10-17 19:52:41</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788001626</t>
+          <t>788009096</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carlos1995</t>
+          <t>royser123</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-10-14 22:28:58</t>
+          <t>2025-10-17 20:00:55</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788001635</t>
+          <t>788009102</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Carolinaa</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>S/20.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-10-14 22:50:16</t>
+          <t>2025-10-17 20:05:43</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788001653</t>
+          <t>788009111</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hebercabrera</t>
+          <t>yovera92</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-10-14 23:21:27</t>
+          <t>2025-10-17 20:11:40</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788001659</t>
+          <t>788009177</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jyauri094</t>
+          <t>thejotaf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S/1.61</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-10-14 23:31:32</t>
+          <t>2025-10-17 22:16:45</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>788001668</t>
+          <t>788009195</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>brayer1991</t>
+          <t>Gjelo777</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-10-15 00:13:14</t>
+          <t>2025-10-17 22:41:58</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>788001986</t>
+          <t>788009213</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lasro</t>
+          <t>aprilpaz</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-10-15 06:46:43</t>
+          <t>2025-10-17 22:53:25</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>788002055</t>
+          <t>788009246</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>lui</t>
+          <t>Matteo1727</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-10-15 07:38:19</t>
+          <t>2025-10-18 00:33:04</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>788002124</t>
+          <t>788009465</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kevinparedes21</t>
+          <t>943301374</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-10-15 08:06:21</t>
+          <t>2025-10-18 04:53:27</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>788002271</t>
+          <t>788009678</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lexisma</t>
+          <t>Jdarlin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-10-15 08:56:06</t>
+          <t>2025-10-18 06:21:17</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>788002556</t>
+          <t>788009801</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tigre0987</t>
+          <t>wilbert</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2025-10-15 10:06:17</t>
+          <t>2025-10-18 07:03:29</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>788002709</t>
+          <t>788009915</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dianabel</t>
+          <t>amoralesv</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-10-15 10:39:31</t>
+          <t>2025-10-18 07:35:35</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>788003142</t>
+          <t>788010224</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IsidoroXD</t>
+          <t>kilmervillar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/40.00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-10-15 12:32:56</t>
+          <t>2025-10-18 08:37:35</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>788003288</t>
+          <t>788010335</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>elmer.subiate</t>
+          <t>Elizabethaviles</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/50.00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-10-15 13:28:17</t>
+          <t>2025-10-18 08:54:23</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>788003375</t>
+          <t>788010407</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>julianapaz</t>
+          <t>trebla9813</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2025-10-15 14:05:39</t>
+          <t>2025-10-18 09:08:56</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>788003408</t>
+          <t>788010569</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>smith11</t>
+          <t>taniamoreno</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/191.00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2025-10-15 14:26:51</t>
+          <t>2025-10-18 09:49:41</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>788003429</t>
+          <t>788010590</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Anthony0815</t>
+          <t>celiasalazar</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-10-15 14:41:13</t>
+          <t>2025-10-18 09:54:37</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>788003480</t>
+          <t>788010731</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jimmisaavedraguevara</t>
+          <t>jaimefernandez22</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-10-15 15:34:26</t>
+          <t>2025-10-18 10:23:39</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>788003486</t>
+          <t>788010827</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Joseleon39</t>
+          <t>Marcelo21</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2025-10-15 15:36:13</t>
+          <t>2025-10-18 10:55:07</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>788003513</t>
+          <t>788010926</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>pres</t>
+          <t>lokito1991</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2025-10-15 15:56:20</t>
+          <t>2025-10-18 11:10:26</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>788003522</t>
+          <t>788011196</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>manuel1996</t>
+          <t>abvulinho</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2025-10-15 15:59:42</t>
+          <t>2025-10-18 12:08:16</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>788003534</t>
+          <t>788011496</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>helenrr</t>
+          <t>Jannike350928</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2025-10-15 16:11:12</t>
+          <t>2025-10-18 13:25:14</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2784,12 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>788003561</t>
+          <t>788011532</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richard1986</t>
+          <t>jorge.luis</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2025-10-15 16:22:33</t>
+          <t>2025-10-18 13:33:17</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2832,12 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>788003603</t>
+          <t>788011577</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>klibertev</t>
+          <t>manuelpumacayo01</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2025-10-15 16:44:51</t>
+          <t>2025-10-18 13:58:06</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>788003705</t>
+          <t>788011598</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>judith19</t>
+          <t>Davidm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2025-10-15 17:29:51</t>
+          <t>2025-10-18 14:06:14</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2928,12 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>788003729</t>
+          <t>788011625</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>betbet123</t>
+          <t>yeems</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2025-10-15 17:39:37</t>
+          <t>2025-10-18 14:21:26</t>
         </is>
       </c>
     </row>
@@ -2976,12 +2976,12 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>788003759</t>
+          <t>788011679</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>75705801</t>
+          <t>Carlitoso95</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2025-10-15 18:15:59</t>
+          <t>2025-10-18 14:47:54</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>788003762</t>
+          <t>788011697</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>luisino</t>
+          <t>Alfretcr</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2025-10-15 18:16:09</t>
+          <t>2025-10-18 15:02:57</t>
         </is>
       </c>
     </row>
@@ -3072,12 +3072,12 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>788003768</t>
+          <t>788011703</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>neni22</t>
+          <t>Adrian05</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2025-10-15 18:20:43</t>
+          <t>2025-10-18 15:03:44</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>788003846</t>
+          <t>788011709</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>maritza</t>
+          <t>Fransar</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2025-10-15 19:54:17</t>
+          <t>2025-10-18 15:04:23</t>
         </is>
       </c>
     </row>
@@ -3168,12 +3168,12 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>788003885</t>
+          <t>788011724</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>tablarock</t>
+          <t>CLAUDIA0125</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2025-10-15 20:34:19</t>
+          <t>2025-10-18 15:12:23</t>
         </is>
       </c>
     </row>
@@ -3216,12 +3216,12 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>788003912</t>
+          <t>788011871</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>leymer</t>
+          <t>Anabeli</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2025-10-15 21:12:30</t>
+          <t>2025-10-18 17:08:31</t>
         </is>
       </c>
     </row>
@@ -3264,12 +3264,12 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>788003933</t>
+          <t>788011874</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>fang47</t>
+          <t>pablo777789</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2025-10-15 22:41:57</t>
+          <t>2025-10-18 17:12:01</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3312,12 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>788003954</t>
+          <t>788011916</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jairpaifa</t>
+          <t>RAMIREZ22</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2025-10-15 23:05:21</t>
+          <t>2025-10-18 17:33:22</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3360,12 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>788003960</t>
+          <t>788012000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>victor1677</t>
+          <t>JULIOQUI21</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3400,7 +3400,2503 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2025-10-15 23:21:09</t>
+          <t>2025-10-18 18:36:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788012027</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LUISALBERTO_01</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-10-18 18:53:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788012033</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CALLE_2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-10-18 18:57:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788012039</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>juanpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-10-18 18:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788012069</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jhordy.paul</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-10-18 19:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788012081</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FREDDY_2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-10-18 19:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788012087</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Yasss88</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-10-18 19:38:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788012090</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Carlitosss14</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-10-18 19:41:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788012102</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>maquita01</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-10-18 20:05:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788012192</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-10-18 21:46:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788012195</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jesusito190927</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-10-18 21:47:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788012213</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>aubert</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-10-18 22:14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788012222</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chefico</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.40</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-10-18 22:22:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788012225</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>james26</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-10-18 22:33:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788012264</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Alexgianfranco3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-10-19 00:15:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788012279</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>pato125</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-10-19 01:12:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788012300</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Wendy2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-10-19 01:45:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788012585</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>78461353G</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-10-19 06:00:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788012606</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>silvapradoelmer</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-10-19 06:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788012666</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Jarvis</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-10-19 06:33:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788012750</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Aa1306</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-10-19 07:01:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788012822</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>nolbert1713</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-10-19 07:25:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788012975</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Quintero.pacheco</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-10-19 08:21:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788013170</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>elganador1979</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-10-19 09:14:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788013242</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cris6513</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-10-19 09:34:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788013251</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>JEANPIERE03</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-10-19 09:36:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788013269</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PEDRO81</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-10-19 09:44:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788013392</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>chiztrizz</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-10-19 10:15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788013428</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ronal.quintana</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-10-19 10:27:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788013614</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PAUL01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-10-19 11:25:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788013620</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Seidab</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-10-19 11:27:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788013644</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>JIMY02</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-10-19 11:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788013740</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mat_21</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-10-19 12:19:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788013884</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>agimael.shpukat</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-10-19 13:13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788013932</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>alexander06.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-10-19 13:28:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788013935</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>RAULYARLEQUE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-10-19 13:29:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>788013959</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>justus1616</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-10-19 13:37:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>788013968</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>celiafp28</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/55.75</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-10-19 13:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>788013977</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>crober</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2025-10-19 13:42:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>788014010</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>972107272</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2025-10-19 14:10:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>788014088</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ichc2025</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2025-10-19 14:56:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>788014178</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PainYahi07</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2025-10-19 16:16:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>788014268</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>marip</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2025-10-19 17:24:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>788014322</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>LUISDAVILA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2025-10-19 18:08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>788014346</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>fran2194</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2025-10-19 18:32:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>788014355</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ros</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2025-10-19 18:36:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>788014385</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Eddy06</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S/20.00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2025-10-19 19:20:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>788014430</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>lopeza28</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2025-10-19 20:12:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>788014433</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Liset</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2025-10-19 20:15:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>788014472</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>chikito38</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2025-10-19 21:24:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>788014478</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>milano</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2025-10-19 21:27:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>788014520</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Duque550</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S/0.72</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2025-10-19 22:10:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>788014565</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>meliza2706</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2025-10-19 23:24:10</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788034644</t>
+          <t>788037476</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GALAXIA777</t>
+          <t>Manuel198202</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-10-27 00:12:14</t>
+          <t>2025-10-28 00:02:06</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788034833</t>
+          <t>788037491</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jerson17cm</t>
+          <t>rulito</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-10-27 05:27:19</t>
+          <t>2025-10-28 00:46:08</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788035136</t>
+          <t>788037494</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>josetamarony</t>
+          <t>juanballena</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-10-27 07:28:30</t>
+          <t>2025-10-28 01:16:51</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788035460</t>
+          <t>788037500</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kekolit13</t>
+          <t>abelitoz</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-10-27 09:03:40</t>
+          <t>2025-10-28 01:26:54</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788035595</t>
+          <t>788037506</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>castaneda25</t>
+          <t>percyrg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/50.33</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-27 09:38:07</t>
+          <t>2025-10-28 01:45:02</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788035661</t>
+          <t>788037512</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Juliorodri</t>
+          <t>usksma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-10-27 09:47:37</t>
+          <t>2025-10-28 01:51:57</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788035931</t>
+          <t>788037524</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>robertoquispe03</t>
+          <t>smith.rt259</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-10-27 10:46:28</t>
+          <t>2025-10-28 02:24:46</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788035991</t>
+          <t>788037767</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gabrielito</t>
+          <t>maridey</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-10-27 10:59:19</t>
+          <t>2025-10-28 06:16:02</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788036081</t>
+          <t>788038517</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chef14</t>
+          <t>OLACIO65</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-27 11:28:39</t>
+          <t>2025-10-28 10:07:03</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788036300</t>
+          <t>788038571</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jrcapchita</t>
+          <t>quintero03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-10-27 12:18:54</t>
+          <t>2025-10-28 10:23:31</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788036642</t>
+          <t>788038634</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yonair</t>
+          <t>Cherito12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-27 13:39:49</t>
+          <t>2025-10-28 10:42:52</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788036675</t>
+          <t>788038829</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>tolking1818</t>
+          <t>eder230792</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-10-27 14:07:03</t>
+          <t>2025-10-28 11:31:33</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788036711</t>
+          <t>788038916</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>yimil</t>
+          <t>kriki</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-10-27 14:21:24</t>
+          <t>2025-10-28 11:47:27</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788036714</t>
+          <t>788039045</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>billy2907</t>
+          <t>Remdiw44</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S/449.54</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-10-27 14:21:45</t>
+          <t>2025-10-28 12:04:14</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788036744</t>
+          <t>788039252</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>meli89</t>
+          <t>gatita77</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-10-27 14:35:08</t>
+          <t>2025-10-28 12:59:16</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788036756</t>
+          <t>788039303</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cristhian512</t>
+          <t>Dustellar</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-10-27 14:38:42</t>
+          <t>2025-10-28 13:10:42</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788036765</t>
+          <t>788039306</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kevinmgd95</t>
+          <t>IsabellaSR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/8.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-10-27 14:40:11</t>
+          <t>2025-10-28 13:11:53</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788036888</t>
+          <t>788039423</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>karlo1944</t>
+          <t>Cristhiang.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-27 15:45:57</t>
+          <t>2025-10-28 13:46:34</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788036975</t>
+          <t>788039630</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>drak</t>
+          <t>guti_ez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-27 16:17:59</t>
+          <t>2025-10-28 15:19:13</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788037047</t>
+          <t>788039645</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>samuelpari29</t>
+          <t>maykeljjk</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-27 16:47:08</t>
+          <t>2025-10-28 15:25:07</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788037302</t>
+          <t>788039657</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hen26</t>
+          <t>vero_123</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-10-27 20:15:09</t>
+          <t>2025-10-28 15:38:11</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788037374</t>
+          <t>788039684</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wily11</t>
+          <t>ebert13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-27 21:32:56</t>
+          <t>2025-10-28 15:58:26</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788037389</t>
+          <t>788039687</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yossig</t>
+          <t>aleco</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/0.34</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-27 21:47:32</t>
+          <t>2025-10-28 15:59:37</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788037416</t>
+          <t>788039768</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>romantico.50</t>
+          <t>yango</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-27 22:16:40</t>
+          <t>2025-10-28 16:37:40</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788037437</t>
+          <t>788039861</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cristhofer123</t>
+          <t>jose005</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S/1,300.56</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-27 22:52:10</t>
+          <t>2025-10-28 17:20:33</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788037452</t>
+          <t>788040152</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yoelc.s</t>
+          <t>jmgutierrez</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/5.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-10-27 23:07:50</t>
+          <t>2025-10-28 19:30:42</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788037473</t>
+          <t>788040257</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>adolfin777</t>
+          <t>maripili</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,199 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-10-27 23:56:17</t>
+          <t>2025-10-28 21:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788040263</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ale23</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-10-28 21:05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788040293</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>iraida12</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-10-28 22:00:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788040356</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Anely</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-10-28 23:51:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788040359</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>luisito30</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-10-28 23:54:10</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788037476</t>
+          <t>788043881</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manuel198202</t>
+          <t>mirkogr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-10-28 00:02:06</t>
+          <t>2025-10-30 00:09:49</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788037491</t>
+          <t>788043905</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rulito</t>
+          <t>cesar1022</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.68</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-10-28 00:46:08</t>
+          <t>2025-10-30 00:46:23</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788037494</t>
+          <t>788044070</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>juanballena</t>
+          <t>jjjordan18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.66</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-10-28 01:16:51</t>
+          <t>2025-10-30 04:52:33</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788037500</t>
+          <t>788044448</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abelitoz</t>
+          <t>cristian.10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-10-28 01:26:54</t>
+          <t>2025-10-30 07:40:44</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788037506</t>
+          <t>788044559</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>percyrg</t>
+          <t>jaqui</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/50.33</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-28 01:45:02</t>
+          <t>2025-10-30 08:10:45</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788037512</t>
+          <t>788044610</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>usksma</t>
+          <t>FELIXHUMBERTO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-10-28 01:51:57</t>
+          <t>2025-10-30 08:38:01</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788037524</t>
+          <t>788044721</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>smith.rt259</t>
+          <t>Flavio01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-10-28 02:24:46</t>
+          <t>2025-10-30 09:35:49</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788037767</t>
+          <t>788044919</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>maridey</t>
+          <t>ANDRETI18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-10-28 06:16:02</t>
+          <t>2025-10-30 11:07:34</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788038517</t>
+          <t>788044943</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OLACIO65</t>
+          <t>Connie44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-28 10:07:03</t>
+          <t>2025-10-30 11:16:58</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788038571</t>
+          <t>788045174</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quintero03</t>
+          <t>Juancho28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-10-28 10:23:31</t>
+          <t>2025-10-30 12:45:46</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788038634</t>
+          <t>788045183</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cherito12</t>
+          <t>yngonzalo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-28 10:42:52</t>
+          <t>2025-10-30 12:47:22</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788038829</t>
+          <t>788045201</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eder230792</t>
+          <t>golver</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S/0.09</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-10-28 11:31:33</t>
+          <t>2025-10-30 12:55:51</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788038916</t>
+          <t>788045246</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kriki</t>
+          <t>Jpjim</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-10-28 11:47:27</t>
+          <t>2025-10-30 13:17:24</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788039045</t>
+          <t>788045324</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remdiw44</t>
+          <t>ela08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-10-28 12:04:14</t>
+          <t>2025-10-30 13:52:10</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788039252</t>
+          <t>788045336</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gatita77</t>
+          <t>lolaxlola1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-10-28 12:59:16</t>
+          <t>2025-10-30 13:57:37</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788039303</t>
+          <t>788045423</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dustellar</t>
+          <t>Beyker</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-10-28 13:10:42</t>
+          <t>2025-10-30 14:38:34</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788039306</t>
+          <t>788045480</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IsabellaSR</t>
+          <t>alfonso08</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S/8.00</t>
+          <t>S/0.24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-10-28 13:11:53</t>
+          <t>2025-10-30 15:06:28</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788039423</t>
+          <t>788045525</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cristhiang.</t>
+          <t>Matabby2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-28 13:46:34</t>
+          <t>2025-10-30 15:27:48</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788039630</t>
+          <t>788045639</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>guti_ez</t>
+          <t>Joshua140803</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-28 15:19:13</t>
+          <t>2025-10-30 16:24:35</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788039645</t>
+          <t>788045789</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>maykeljjk</t>
+          <t>nicoelrico1331</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-28 15:25:07</t>
+          <t>2025-10-30 17:50:17</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788039657</t>
+          <t>788045816</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>vero_123</t>
+          <t>ANTONS123</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-10-28 15:38:11</t>
+          <t>2025-10-30 18:10:11</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788039684</t>
+          <t>788045954</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ebert13</t>
+          <t>luis47</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-28 15:58:26</t>
+          <t>2025-10-30 20:55:43</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788039687</t>
+          <t>788045966</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>aleco</t>
+          <t>PIANKI-18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-28 15:59:37</t>
+          <t>2025-10-30 21:17:37</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788039768</t>
+          <t>788045987</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yango</t>
+          <t>PERES123</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-28 16:37:40</t>
+          <t>2025-10-30 21:36:18</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788039861</t>
+          <t>788045999</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jose005</t>
+          <t>derian</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-28 17:20:33</t>
+          <t>2025-10-30 21:44:04</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788040152</t>
+          <t>788046020</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jmgutierrez</t>
+          <t>David_allka</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S/5.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-10-28 19:30:42</t>
+          <t>2025-10-30 21:56:15</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788040257</t>
+          <t>788046041</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>maripili</t>
+          <t>aguinda</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-10-28 21:01:33</t>
+          <t>2025-10-30 22:25:49</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788040263</t>
+          <t>788046065</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ale23</t>
+          <t>alejandrari</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-10-28 21:05:47</t>
+          <t>2025-10-30 23:15:43</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788040293</t>
+          <t>788046074</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>iraida12</t>
+          <t>YOUSS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-10-28 22:00:40</t>
+          <t>2025-10-30 23:22:41</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788040356</t>
+          <t>788046089</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Anely</t>
+          <t>Omar30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-10-28 23:51:02</t>
+          <t>2025-10-30 23:52:36</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788040359</t>
+          <t>788046092</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>luisito30</t>
+          <t>yusbel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,7447 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-10-28 23:54:10</t>
+          <t>2025-10-30 23:56:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788046104</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Manuelrc10</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:21:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788046110</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ulises777a</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:29:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788046146</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Josebostin</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-10-31 01:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788046413</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>martinmen10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/30.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-10-31 08:21:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788046495</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Xusterio</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-10-31 08:51:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788046499</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gimena13</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-10-31 08:53:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788046501</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>juniorciro</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-10-31 08:53:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788046787</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Walter12345</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-10-31 10:35:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788047053</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MONICA0830</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.24</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-10-31 12:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788047063</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ARTUROgamarra23</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-10-31 12:04:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788047251</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bryanxxv25</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-10-31 13:14:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788047289</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jose2103</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-10-31 13:24:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788047307</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Anthony1096</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-10-31 13:30:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788047503</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fla23</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:43:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788047509</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>herodetri</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:50:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788047515</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>juandavidyc</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788047519</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Alex7854</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-10-31 16:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788047645</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>yedu95</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-10-31 18:12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788047707</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>eytan</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-10-31 20:46:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788047709</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Onecimo</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-10-31 20:55:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788047711</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>muse222426</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-10-31 20:56:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788047731</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Jyuya</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-10-31 21:52:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788047745</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>samuel26</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-10-31 22:03:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788047747</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>eduardo282828</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-10-31 22:12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788047765</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kevin00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.70</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-10-31 22:51:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788047769</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>cturpoq</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/45.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-10-31 22:59:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788047790</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Carolina3</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-11-01 00:08:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788047796</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jaximusap</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-11-01 00:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788047817</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>kari</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-11-01 00:58:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788047841</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rogersanchez</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-11-01 01:31:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788047850</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>934997689</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-11-01 01:41:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788048258</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>omardavid</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.03</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-11-01 07:07:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788048417</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>mateomartel</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-11-01 07:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788048462</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>alexarteaga</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-11-01 08:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788048831</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>luismiguel01</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-11-01 09:28:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788048840</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jasanber</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.13</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-11-01 09:29:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788048882</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>cristianiglesias</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-11-01 09:43:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788049665</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>lecaiq</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-11-01 14:05:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788049683</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>garfell</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-11-01 14:15:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788049710</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>juandiegopb98</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/254.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-11-01 14:33:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788049824</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Axelalessandro</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-11-01 15:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788049848</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Jcaceres</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-11-01 15:38:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788049893</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MOUSTAKAS01</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/61.25</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-11-01 15:55:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788049926</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>GianmarcoyBeverly</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-11-01 16:23:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788049977</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Franco777</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.03</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-11-01 17:05:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788049995</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Exgar</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-11-01 17:17:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788050025</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>alexacalin</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-11-01 17:34:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788050127</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>STR3ICK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-11-01 19:22:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788050181</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jc100377</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-11-01 20:19:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788050193</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>katylis</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-11-01 20:29:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788050196</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Brayanchumacero</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-11-01 20:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788050211</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Emi</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-11-01 20:45:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788050220</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>OLEMAR43</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-11-01 20:52:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788050226</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OTONIEL05</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-11-01 20:57:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788050235</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CESAR48</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-11-01 21:08:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788050256</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>daaamichin</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-11-01 21:47:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788050283</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Axelramoshs2000</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-11-01 22:13:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788050313</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HEVER</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-11-01 23:02:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788050322</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>pedrito12345</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.19</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-11-01 23:09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788050346</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>antonycisneros</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-11-01 23:29:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788050358</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>blasandy1111</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-11-01 23:40:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788050445</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ayazabdielyapura</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-11-02 03:08:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788050466</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>45961244</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-11-02 03:30:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788050478</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>luiwi</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-11-02 03:46:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788050709</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Yohony</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-11-02 06:26:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>788050802</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Luisgolac28</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-11-02 06:58:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>788050884</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>chiki42</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-11-02 08:22:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>788050890</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>sofiadss</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2025-11-02 08:26:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>788051054</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>angelcordova</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2025-11-02 10:17:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>788051087</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>zuniga2025</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2025-11-02 10:29:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>788051165</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ema200511</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2025-11-02 11:12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>788051234</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>juanka33</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2025-11-02 11:35:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>788051291</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>emir</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2025-11-02 12:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>788051312</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>jhey</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S/14.64</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2025-11-02 12:21:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>788051423</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>diegot21</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2025-11-02 13:32:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>788051612</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>joseleyner</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2025-11-02 15:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>788051621</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>memin</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2025-11-02 15:07:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>788051696</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>gary023025</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2025-11-02 16:07:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>788051747</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>castillo25</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2025-11-02 16:54:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>788051786</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Jhonatansolano10</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2025-11-02 17:19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>788051816</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>lucerooo</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2025-11-02 17:36:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>788051828</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>irma1608</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2025-11-02 17:50:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>788051870</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fernando7705</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2025-11-02 18:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>788051873</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>torr</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2025-11-02 18:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>788051924</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>rumaldo</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2025-11-02 19:06:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>788051927</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2929Vita</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2025-11-02 19:10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>788051930</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Yuliers19</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>S/0.32</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2025-11-02 19:11:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>788051936</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>puchi21</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2025-11-02 19:13:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>788051948</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>esca</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2025-11-02 19:24:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>788051969</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cristia</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2025-11-02 19:45:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>788051975</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fernandogabriel31</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2025-11-02 19:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>788051996</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Mayraquiro</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2025-11-02 20:15:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>788051999</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>navar106</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>S/0.46</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2025-11-02 20:16:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>788052014</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>davilaquispelizeth</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2025-11-02 20:38:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>788052020</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gladys29</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2025-11-02 20:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>788052056</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>juliex</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2025-11-02 21:45:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>788052065</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jlkd</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2025-11-02 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>788052089</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Jhoanjorje37</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2025-11-02 22:35:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>788052131</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>pedrogavidia</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>788052146</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Elas</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:49:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>788052161</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>48247396</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2025-11-03 01:12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>788052164</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Henryleon47</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2025-11-03 01:13:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>788052170</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tiago20zz</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2025-11-03 01:29:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>788052185</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Junior2001</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2025-11-03 02:15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>788052218</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Alonso04</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>S/841.00</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2025-11-03 03:24:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>788052224</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>elmergordillo99</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2025-11-03 03:30:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>788052452</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Hitman</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2025-11-03 06:44:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>788052593</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>eswin234</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2025-11-03 07:22:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>788052620</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Darey31a</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2025-11-03 07:24:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>788052644</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>per75</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2025-11-03 07:29:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>788053013</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>kathaleya</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2025-11-03 09:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>788053067</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>edgarlozanotorres9</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2025-11-03 09:20:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>788053133</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Pelikan23</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2025-11-03 09:34:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>788053145</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Pnp</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2025-11-03 09:38:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>788053265</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>sant</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2025-11-03 10:02:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>788053340</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>inpiyba2025</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2025-11-03 10:15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>788053691</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>yanjj</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2025-11-03 11:30:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>788053868</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Josep</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2025-11-03 12:06:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>788054186</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>LUISF01</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2025-11-03 13:13:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>788054279</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>vamos</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2025-11-03 13:32:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>788054396</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>112233</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2025-11-03 14:14:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>788054459</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>bella</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2025-11-03 14:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>788054498</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>jheyzon</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2025-11-03 15:06:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>788054561</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>jason86</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2025-11-03 16:00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>788054585</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Rosa.06</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2025-11-03 16:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>788054720</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>fernanda2001</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2025-11-03 17:52:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>788054732</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>max.elvisflo</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2025-11-03 17:59:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>788054744</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>nlimache59</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:05:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>788054762</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PEDROARA</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:18:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>788054768</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Jerson4343</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:26:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>788054774</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>egdar</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:29:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>788054783</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>CESARIDROGO</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:34:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>788054804</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MARCELINO01</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:39:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>788054807</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>JUNIORLOPEZ</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:41:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>788054810</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ancash</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:43:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>788054816</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>JAVIERPALACIOS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2025-11-03 18:46:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>788054882</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>stick123</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>S/18.00</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>788054921</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>tihuayro123</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:45:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>788054924</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sjdkdkdofoekekk</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:45:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>788054927</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>acedson6</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:48:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>788054933</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Bryan2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:03:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>788054954</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Xime13</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:17:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>788054957</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Abelvillegas</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:19:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>788054963</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Angelvilela</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>788054972</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>celedonio07</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:32:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>788054975</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Kenyirm</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:36:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>788054978</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>janck0405</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:42:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>788054987</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>pedro13</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>788055002</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>albertj</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2025-11-03 21:00:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>788055050</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Borrego12</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>S/10.07</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2025-11-03 22:13:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>788055071</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Deiman1992</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2025-11-03 22:52:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>788055086</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>75656164</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2025-11-03 23:14:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>788055098</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Fiore2828</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>2025-11-03 23:39:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>788055104</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Chofi</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>2025-11-03 23:43:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>788055107</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Plikplik123</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>S/0.50</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2025-11-03 23:47:15</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788055122</t>
+          <t>788060477</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sahuar</t>
+          <t>Luisabdiel199320.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-04 00:20:27</t>
+          <t>2025-11-06 00:20:46</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788055599</t>
+          <t>788060501</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>yoma111111</t>
+          <t>537155</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-04 06:36:42</t>
+          <t>2025-11-06 00:51:19</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788055623</t>
+          <t>788060504</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jhonsen</t>
+          <t>Pilarsita15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-04 06:47:35</t>
+          <t>2025-11-06 01:03:42</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788055638</t>
+          <t>788060516</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>deyvis_valdez</t>
+          <t>pastora26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-04 06:58:28</t>
+          <t>2025-11-06 01:50:13</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788055695</t>
+          <t>788060831</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alexande3239</t>
+          <t>Alexasencios</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-04 07:09:56</t>
+          <t>2025-11-06 06:32:17</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788055776</t>
+          <t>788060891</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LEIXYMAR20</t>
+          <t>Rogelio2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-04 07:38:59</t>
+          <t>2025-11-06 06:51:03</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788055950</t>
+          <t>788061059</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nayeli123</t>
+          <t>rhafiki</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/100.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-04 08:36:15</t>
+          <t>2025-11-06 07:36:35</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788055977</t>
+          <t>788061395</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PACHECO2025</t>
+          <t>oney</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-04 08:48:56</t>
+          <t>2025-11-06 08:36:51</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788056061</t>
+          <t>788061470</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>luispalomi</t>
+          <t>75231537</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-04 09:35:04</t>
+          <t>2025-11-06 08:57:25</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788056103</t>
+          <t>788061581</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yeicodark</t>
+          <t>Pacho987</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-04 10:12:55</t>
+          <t>2025-11-06 09:27:45</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788056109</t>
+          <t>788062193</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nicol1501</t>
+          <t>Marvinis</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-04 10:14:21</t>
+          <t>2025-11-06 11:21:10</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788056127</t>
+          <t>788062361</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rohit_sosa</t>
+          <t>fretel18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-04 10:25:44</t>
+          <t>2025-11-06 11:50:47</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788056139</t>
+          <t>788062514</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>952998583</t>
+          <t>Elvisjanampa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-04 10:31:06</t>
+          <t>2025-11-06 12:23:40</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788056142</t>
+          <t>788062703</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Erick-cm</t>
+          <t>PAZOS1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-04 10:31:31</t>
+          <t>2025-11-06 13:11:53</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788056145</t>
+          <t>788062727</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ra</t>
+          <t>MORAN1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-04 10:33:09</t>
+          <t>2025-11-06 13:16:51</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788056166</t>
+          <t>788062733</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luishuerta</t>
+          <t>FERMIN1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-04 10:40:02</t>
+          <t>2025-11-06 13:19:10</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788056190</t>
+          <t>788062925</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vasqu</t>
+          <t>Diani</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-04 10:48:47</t>
+          <t>2025-11-06 14:32:39</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788056199</t>
+          <t>788062928</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>davidleondjlq</t>
+          <t>luialberto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-04 10:56:30</t>
+          <t>2025-11-06 14:33:27</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788056205</t>
+          <t>788063051</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cesarapg</t>
+          <t>yosmery</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-04 10:59:59</t>
+          <t>2025-11-06 15:55:42</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788056247</t>
+          <t>788063057</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WILLIAN81</t>
+          <t>JHON25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-04 11:18:47</t>
+          <t>2025-11-06 16:01:13</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788056523</t>
+          <t>788063069</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>issal32</t>
+          <t>jheyma1235</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-04 12:57:55</t>
+          <t>2025-11-06 16:04:26</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788056661</t>
+          <t>788063081</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hanzella</t>
+          <t>WILSON25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-04 13:40:51</t>
+          <t>2025-11-06 16:08:39</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788056823</t>
+          <t>788063087</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jorge.serrato</t>
+          <t>GIAMPOOL05</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-04 14:24:36</t>
+          <t>2025-11-06 16:11:22</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788056832</t>
+          <t>788063093</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jagp</t>
+          <t>ALBERTO25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-04 14:27:42</t>
+          <t>2025-11-06 16:15:45</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788056856</t>
+          <t>788063099</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MarquitosHub</t>
+          <t>ANTON25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-04 14:34:19</t>
+          <t>2025-11-06 16:20:01</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788056859</t>
+          <t>788063105</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BlackMamba</t>
+          <t>GIAN26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-04 14:38:06</t>
+          <t>2025-11-06 16:23:57</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788056865</t>
+          <t>788063111</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>joseincotrina</t>
+          <t>CRISTOBAL06</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-04 14:38:41</t>
+          <t>2025-11-06 16:27:26</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788056928</t>
+          <t>788063117</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>eduardo1973</t>
+          <t>JELSIN06</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-04 15:15:22</t>
+          <t>2025-11-06 16:33:07</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788057096</t>
+          <t>788063138</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Diego2103</t>
+          <t>EDITH26</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-04 16:24:06</t>
+          <t>2025-11-06 16:37:53</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788057123</t>
+          <t>788063156</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>meza22</t>
+          <t>JONATHAN25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-04 16:46:15</t>
+          <t>2025-11-06 16:50:23</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788057141</t>
+          <t>788063162</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paul546</t>
+          <t>Kath</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/15.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-04 16:56:12</t>
+          <t>2025-11-06 16:54:21</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>788057240</t>
+          <t>788063222</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>elprota40</t>
+          <t>sebas94</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-11-04 17:38:32</t>
+          <t>2025-11-06 17:22:17</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>788057324</t>
+          <t>788063249</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>polita1946</t>
+          <t>Luigui97</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-11-04 18:13:13</t>
+          <t>2025-11-06 17:39:14</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>788057420</t>
+          <t>788063264</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AndyJair</t>
+          <t>gouk18</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-11-04 19:19:54</t>
+          <t>2025-11-06 17:51:03</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>788057426</t>
+          <t>788063339</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jardinero</t>
+          <t>JOELPANTA25</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-11-04 19:32:29</t>
+          <t>2025-11-06 18:48:55</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>788057501</t>
+          <t>788063342</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Angel2425</t>
+          <t>Melina18</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-11-04 20:08:08</t>
+          <t>2025-11-06 18:50:02</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>788057519</t>
+          <t>788063360</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jorgetouzett</t>
+          <t>Maicol_77</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2025-11-04 20:31:03</t>
+          <t>2025-11-06 18:59:48</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>788057531</t>
+          <t>788063372</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>anderson08</t>
+          <t>JJvicio</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-11-04 20:46:45</t>
+          <t>2025-11-06 19:12:55</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>788057558</t>
+          <t>788063381</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>karencs</t>
+          <t>Baca12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-11-04 21:12:47</t>
+          <t>2025-11-06 19:20:09</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>788057561</t>
+          <t>788063453</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jeffray777</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/18.00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-11-04 21:13:48</t>
+          <t>2025-11-06 20:20:10</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>788057585</t>
+          <t>788063513</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>diegxio</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2025-11-04 22:02:51</t>
+          <t>2025-11-06 22:01:21</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>788057615</t>
+          <t>788063534</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hemer88</t>
+          <t>905959320</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2025-11-04 22:40:45</t>
+          <t>2025-11-06 22:28:13</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>788057621</t>
+          <t>788063543</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZENFER70</t>
+          <t>comando.95</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-11-04 22:56:06</t>
+          <t>2025-11-06 22:34:58</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>788057639</t>
+          <t>788063549</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Copito12</t>
+          <t>jch24</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2584,7 +2584,55 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-11-04 23:34:26</t>
+          <t>2025-11-06 22:44:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788063561</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DONADOR1234</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-11-06 22:56:05</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788060477</t>
+          <t>788063606</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luisabdiel199320.</t>
+          <t>Nelcy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-06 00:20:46</t>
+          <t>2025-11-07 01:43:41</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788060501</t>
+          <t>788063609</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>537155</t>
+          <t>anderzon9210</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-06 00:51:19</t>
+          <t>2025-11-07 01:44:34</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788060504</t>
+          <t>788063744</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pilarsita15</t>
+          <t>nanna</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-06 01:03:42</t>
+          <t>2025-11-07 04:49:48</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788060516</t>
+          <t>788063891</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pastora26</t>
+          <t>Manuel199111</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-06 01:50:13</t>
+          <t>2025-11-07 05:53:59</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788060831</t>
+          <t>788063906</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alexasencios</t>
+          <t>mendieta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-06 06:32:17</t>
+          <t>2025-11-07 05:56:46</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788060891</t>
+          <t>788063981</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rogelio2</t>
+          <t>DarkMan23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-06 06:51:03</t>
+          <t>2025-11-07 06:23:12</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788061059</t>
+          <t>788064122</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rhafiki</t>
+          <t>hectorms18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-06 07:36:35</t>
+          <t>2025-11-07 07:12:17</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788061395</t>
+          <t>788064335</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>oney</t>
+          <t>ivescv</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-06 08:36:51</t>
+          <t>2025-11-07 08:01:35</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788061470</t>
+          <t>788064347</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>75231537</t>
+          <t>naparicio123</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-06 08:57:25</t>
+          <t>2025-11-07 08:04:59</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788061581</t>
+          <t>788064467</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pacho987</t>
+          <t>aylim</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-06 09:27:45</t>
+          <t>2025-11-07 08:29:49</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788062193</t>
+          <t>788065175</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Marvinis</t>
+          <t>joselcruz12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-06 11:21:10</t>
+          <t>2025-11-07 10:59:09</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788062361</t>
+          <t>788065397</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fretel18</t>
+          <t>anlifay</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-06 11:50:47</t>
+          <t>2025-11-07 11:37:37</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788062514</t>
+          <t>788065481</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Elvisjanampa</t>
+          <t>Berrios01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-06 12:23:40</t>
+          <t>2025-11-07 11:48:07</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788062703</t>
+          <t>788065583</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PAZOS1</t>
+          <t>Nztest</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-06 13:11:53</t>
+          <t>2025-11-07 12:09:33</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788062727</t>
+          <t>788065616</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MORAN1</t>
+          <t>Frankmanuyama</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-06 13:16:51</t>
+          <t>2025-11-07 12:15:42</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788062733</t>
+          <t>788065859</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FERMIN1</t>
+          <t>dano2001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-06 13:19:10</t>
+          <t>2025-11-07 13:14:48</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788062925</t>
+          <t>788065904</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diani</t>
+          <t>GUZMANBH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-06 14:32:39</t>
+          <t>2025-11-07 13:22:58</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788062928</t>
+          <t>788066048</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>luialberto</t>
+          <t>Marckjor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-06 14:33:27</t>
+          <t>2025-11-07 13:54:13</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788063051</t>
+          <t>788066084</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yosmery</t>
+          <t>milena</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-06 15:55:42</t>
+          <t>2025-11-07 14:03:33</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788063057</t>
+          <t>788066087</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JHON25</t>
+          <t>Techy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-06 16:01:13</t>
+          <t>2025-11-07 14:04:17</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788063069</t>
+          <t>788066120</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jheyma1235</t>
+          <t>xiomara</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-06 16:04:26</t>
+          <t>2025-11-07 14:15:36</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788063081</t>
+          <t>788066585</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WILSON25</t>
+          <t>GODO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-06 16:08:39</t>
+          <t>2025-11-07 18:25:37</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788063087</t>
+          <t>788066621</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GIAMPOOL05</t>
+          <t>Ander01939</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-06 16:11:22</t>
+          <t>2025-11-07 19:10:23</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788063093</t>
+          <t>788066630</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ALBERTO25</t>
+          <t>sebas19062009</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-06 16:15:45</t>
+          <t>2025-11-07 19:18:05</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788063099</t>
+          <t>788066645</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ANTON25</t>
+          <t>Maxxitto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-06 16:20:01</t>
+          <t>2025-11-07 19:34:12</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788063105</t>
+          <t>788066729</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GIAN26</t>
+          <t>lizandro1996</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-06 16:23:57</t>
+          <t>2025-11-07 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788063111</t>
+          <t>788066735</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CRISTOBAL06</t>
+          <t>46712394</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-06 16:27:26</t>
+          <t>2025-11-07 20:29:54</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788063117</t>
+          <t>788066744</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JELSIN06</t>
+          <t>avata</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-06 16:33:07</t>
+          <t>2025-11-07 20:34:37</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788063138</t>
+          <t>788066753</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EDITH26</t>
+          <t>yaredjaziel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-06 16:37:53</t>
+          <t>2025-11-07 20:39:49</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788063156</t>
+          <t>788066756</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JONATHAN25</t>
+          <t>OSOMAR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-06 16:50:23</t>
+          <t>2025-11-07 20:41:05</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788063162</t>
+          <t>788066786</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kath</t>
+          <t>haniel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S/15.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-06 16:54:21</t>
+          <t>2025-11-07 21:00:24</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>788063222</t>
+          <t>788066843</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sebas94</t>
+          <t>Oscar_2904</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-11-06 17:22:17</t>
+          <t>2025-11-07 22:16:38</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>788063249</t>
+          <t>788066894</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luigui97</t>
+          <t>74694159</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-11-06 17:39:14</t>
+          <t>2025-11-07 23:29:22</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>788063264</t>
+          <t>788066987</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gouk18</t>
+          <t>Ulises99</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-11-06 17:51:03</t>
+          <t>2025-11-08 02:18:57</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>788063339</t>
+          <t>788067089</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JOELPANTA25</t>
+          <t>jheiner</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-11-06 18:48:55</t>
+          <t>2025-11-08 04:20:48</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>788063342</t>
+          <t>788067524</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Melina18</t>
+          <t>Mendo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-11-06 18:50:02</t>
+          <t>2025-11-08 07:05:46</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>788063360</t>
+          <t>788067611</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maicol_77</t>
+          <t>pe300</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2025-11-06 18:59:48</t>
+          <t>2025-11-08 07:29:57</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>788063372</t>
+          <t>788067650</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JJvicio</t>
+          <t>Josemanuel20</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-11-06 19:12:55</t>
+          <t>2025-11-08 07:35:15</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>788063381</t>
+          <t>788067770</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Baca12</t>
+          <t>oayalar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-11-06 19:20:09</t>
+          <t>2025-11-08 08:08:09</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>788063453</t>
+          <t>788067899</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>manzana</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>S/18.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-11-06 20:20:10</t>
+          <t>2025-11-08 08:35:41</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>788063513</t>
+          <t>788067980</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>barruetaaranda</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2025-11-06 22:01:21</t>
+          <t>2025-11-08 08:52:36</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>788063534</t>
+          <t>788068193</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>905959320</t>
+          <t>Euge24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/113.00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2025-11-06 22:28:13</t>
+          <t>2025-11-08 09:36:13</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>788063543</t>
+          <t>788068823</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>comando.95</t>
+          <t>gigi18</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-11-06 22:34:58</t>
+          <t>2025-11-08 11:36:43</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>788063549</t>
+          <t>788068916</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jch24</t>
+          <t>manuelito1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-11-06 22:44:04</t>
+          <t>2025-11-08 11:54:55</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>788063561</t>
+          <t>788068925</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DONADOR1234</t>
+          <t>xinita30</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2632,7 +2632,3175 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2025-11-06 22:56:05</t>
+          <t>2025-11-08 11:59:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788068958</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>manuxlzinnn</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-11-08 12:06:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788069015</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ale.xiot</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-11-08 12:19:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788069228</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Dianlopez</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-11-08 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788069249</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>yose12</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-11-08 13:03:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788069468</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>vivas123</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-11-08 14:01:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788069525</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Jessan</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/5.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-11-08 14:31:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788069588</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LuzVR77</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:02:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788069648</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Kiabeth13</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:33:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788069702</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>giampiers04</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:15:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788069786</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jeffersonn</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-11-08 17:02:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788069834</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Jen510</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-11-08 17:28:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788069894</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Jhonata</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-11-08 18:17:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788069903</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Manuela</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Congelado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-11-08 18:26:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788069918</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Jaimeso</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-11-08 18:40:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788069921</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>maykelwaldir</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-11-08 18:40:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788069945</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cesar2005</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-11-08 19:14:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788069990</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Leeonidas</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-11-08 19:43:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788070029</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>pibe123</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-11-08 20:00:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788070053</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>46328886</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-11-08 20:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788070059</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>harim</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-11-08 20:38:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788070077</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>milicerdan</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-11-08 21:04:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788070104</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>David.tico</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-11-08 22:02:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788070107</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sandris</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-11-08 22:11:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788070173</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dereck2020</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-11-09 00:36:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788070275</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Segundo94</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-11-09 04:11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788070389</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Denber</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-11-09 05:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788070545</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>flakito</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-11-09 06:23:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788070887</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>nose</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-11-09 08:46:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788070950</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>climtonjim</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-11-09 09:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788070992</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Darlig.25</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-11-09 09:38:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788071037</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>josedavidc</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-11-09 09:55:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788071052</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OmarJavier</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-11-09 10:01:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788071091</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>lipushim123</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-11-09 10:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788071190</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sarmiento123</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-11-09 10:58:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788071241</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>dominguez123</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-11-09 11:14:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788071385</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Hemerson</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-11-09 12:21:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788071403</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>crispinluis</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-11-09 12:26:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788071415</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>joelitomiamor</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-11-09 12:35:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788071454</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Nunca</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-11-09 12:46:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788071463</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>taxita</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-11-09 12:49:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788071502</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>alelii</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-11-09 13:04:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788071517</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Kokitosax10</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/70.14</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-11-09 13:09:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788071562</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>demetriocisneros</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-11-09 13:25:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788071670</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Chulucanas2020</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-11-09 14:06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788071694</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Zaidjulca</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-11-09 14:17:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788071700</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>74090732</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/1.40</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-11-09 14:18:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788071772</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Josiahcc3</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-11-09 14:35:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788071802</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>fiore31</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-11-09 14:46:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788071811</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>josemacedo09</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-11-09 14:49:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788071874</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fhkfmf</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-11-09 15:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788071988</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>OTINIANO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/100.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-11-09 16:28:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>788072084</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>POLAR</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-11-09 17:30:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>788072111</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>gerson30</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-11-09 17:46:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>788072144</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tanatozkin12</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2025-11-09 18:19:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>788072174</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>haytana</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2025-11-09 19:01:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>788072198</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>joycri</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2025-11-09 19:20:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>788072210</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Eyal1511</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2025-11-09 19:31:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>788072234</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Fumiko23</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2025-11-09 20:40:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>788072249</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>dayanerosales</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>788072267</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>camilo</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:41:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>788072279</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>rider11</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2025-11-09 22:05:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>788072309</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Manu2729Rosa</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2025-11-09 23:11:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>788072315</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>damaca14</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2025-11-09 23:12:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>788072327</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AlexFernando</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2025-11-09 23:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>788072336</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>reico</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2025-11-09 23:42:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>788072342</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jose1997</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2025-11-09 23:47:14</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788072357</t>
+          <t>788075204</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gladys31</t>
+          <t>Leovargas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-10 01:16:08</t>
+          <t>2025-11-11 00:48:17</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788072663</t>
+          <t>788075207</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Roy18</t>
+          <t>nicho</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-10 06:40:35</t>
+          <t>2025-11-11 00:48:57</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788072912</t>
+          <t>788075228</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chapana21</t>
+          <t>kevinsotobernardo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-10 08:21:49</t>
+          <t>2025-11-11 01:55:45</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788073161</t>
+          <t>788075240</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ever19</t>
+          <t>milagros135</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-10 09:09:07</t>
+          <t>2025-11-11 02:08:11</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788073467</t>
+          <t>788075252</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>aguayo77elias</t>
+          <t>Wuilomio</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-10 10:08:28</t>
+          <t>2025-11-11 02:18:44</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788073545</t>
+          <t>788075414</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gensbong007</t>
+          <t>BENTURA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-10 10:19:05</t>
+          <t>2025-11-11 04:45:56</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788073557</t>
+          <t>788075612</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ronny2025</t>
+          <t>Lguillermo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-10 10:21:04</t>
+          <t>2025-11-11 06:29:14</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788073590</t>
+          <t>788076482</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abelxd12</t>
+          <t>Orlando1268</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-10 10:27:14</t>
+          <t>2025-11-11 09:19:50</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788073707</t>
+          <t>788077028</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>alexxander</t>
+          <t>Beaa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-10 10:51:27</t>
+          <t>2025-11-11 11:10:03</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788073908</t>
+          <t>788077187</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>guille7x</t>
+          <t>brandito97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-10 11:27:21</t>
+          <t>2025-11-11 11:49:39</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788074079</t>
+          <t>788077217</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rodrigo11</t>
+          <t>davidacada</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-10 12:05:33</t>
+          <t>2025-11-11 11:56:53</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788074607</t>
+          <t>788077532</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carla2186</t>
+          <t>Joako</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-10 14:03:47</t>
+          <t>2025-11-11 14:09:13</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788074757</t>
+          <t>788077598</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pao</t>
+          <t>Cabezon1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-10 15:33:31</t>
+          <t>2025-11-11 14:46:04</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788074826</t>
+          <t>788077634</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MickeNVR</t>
+          <t>BRIANNA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-10 16:35:35</t>
+          <t>2025-11-11 14:58:42</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788074859</t>
+          <t>788077676</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>tonyy1111</t>
+          <t>Pablo1987</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-10 17:00:01</t>
+          <t>2025-11-11 15:17:03</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788074895</t>
+          <t>788077715</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Anabel</t>
+          <t>Zahenb</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-10 17:32:19</t>
+          <t>2025-11-11 15:38:32</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788074919</t>
+          <t>788077763</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sariel2710</t>
+          <t>lofra</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-10 17:56:55</t>
+          <t>2025-11-11 15:56:57</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788075024</t>
+          <t>788077778</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JHOAN9</t>
+          <t>ddelaguilatamani</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-10 19:39:27</t>
+          <t>2025-11-11 16:05:59</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788075147</t>
+          <t>788077853</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>gimenezzt</t>
+          <t>Luzcarmen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-10 22:26:17</t>
+          <t>2025-11-11 16:43:16</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788075153</t>
+          <t>788077910</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANMA</t>
+          <t>jesusgonzales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-10 22:46:02</t>
+          <t>2025-11-11 17:17:27</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788075156</t>
+          <t>788077928</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nei4cea</t>
+          <t>Franklin15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-10 22:48:52</t>
+          <t>2025-11-11 17:34:48</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788075174</t>
+          <t>788077934</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TuPaPa11</t>
+          <t>gavaca5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-10 23:23:12</t>
+          <t>2025-11-11 17:36:42</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788075180</t>
+          <t>788077949</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pa1214</t>
+          <t>osito.123</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/60.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,631 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-10 23:29:30</t>
+          <t>2025-11-11 17:49:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>788077967</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Xxkulerokill</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2025-11-11 18:02:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>788077982</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gatito_555</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S/0.20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2025-11-11 18:13:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>788078066</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>40014068</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-11-11 19:29:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>788078096</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Alessia1606</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-11-11 19:49:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788078099</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>daza12</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-11-11 19:54:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788078114</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>cotete0511</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-11-11 20:27:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788078150</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>chemapro123</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-11-11 21:20:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788078168</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>lochibeto23</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-11-11 22:06:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788078171</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jeffreyarmas30</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-11-11 22:14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788078186</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jaykoperu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-11-11 22:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788078195</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Julio82</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-11-11 22:49:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788078210</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>luisvergara</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-11-11 23:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788078225</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>postrador</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-11-11 23:46:51</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788075204</t>
+          <t>788084099</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Leovargas</t>
+          <t>Diego_Calmett</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-11 00:48:17</t>
+          <t>2025-11-14 00:39:33</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788075207</t>
+          <t>788084123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nicho</t>
+          <t>Eduardo246</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-11 00:48:57</t>
+          <t>2025-11-14 01:28:33</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788075228</t>
+          <t>788084198</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kevinsotobernardo</t>
+          <t>crpino17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-11 01:55:45</t>
+          <t>2025-11-14 03:08:23</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788075240</t>
+          <t>788084495</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>milagros135</t>
+          <t>francisco2223</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-11 02:08:11</t>
+          <t>2025-11-14 06:22:39</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788075252</t>
+          <t>788084528</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wuilomio</t>
+          <t>wilito.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-11 02:18:44</t>
+          <t>2025-11-14 06:38:03</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788075414</t>
+          <t>788084612</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BENTURA</t>
+          <t>jheanMar28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-11 04:45:56</t>
+          <t>2025-11-14 07:03:22</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788075612</t>
+          <t>788084966</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lguillermo</t>
+          <t>jhon18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-11 06:29:14</t>
+          <t>2025-11-14 08:25:39</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788076482</t>
+          <t>788084975</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando1268</t>
+          <t>elvencedor13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-11 09:19:50</t>
+          <t>2025-11-14 08:26:08</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788077028</t>
+          <t>788085155</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Beaa</t>
+          <t>waldir07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-11 11:10:03</t>
+          <t>2025-11-14 09:07:11</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788077187</t>
+          <t>788085368</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>brandito97</t>
+          <t>gabyy96</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-11 11:49:39</t>
+          <t>2025-11-14 09:45:01</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788077217</t>
+          <t>788085530</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>davidacada</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-11 11:56:53</t>
+          <t>2025-11-14 10:03:42</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788077532</t>
+          <t>788085752</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Joako</t>
+          <t>ELBRYAN24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-11 14:09:13</t>
+          <t>2025-11-14 10:41:37</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788077598</t>
+          <t>788085830</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cabezon1</t>
+          <t>Orlandoac</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-11 14:46:04</t>
+          <t>2025-11-14 10:53:52</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788077634</t>
+          <t>788086067</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BRIANNA</t>
+          <t>veronika</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-11 14:58:42</t>
+          <t>2025-11-14 11:32:14</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788077676</t>
+          <t>788086151</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pablo1987</t>
+          <t>andersonsixx</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-11 15:17:03</t>
+          <t>2025-11-14 11:47:45</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788077715</t>
+          <t>788086565</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zahenb</t>
+          <t>41802865</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-11 15:38:32</t>
+          <t>2025-11-14 13:25:52</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788077763</t>
+          <t>788086748</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lofra</t>
+          <t>meryesteryup</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-11 15:56:57</t>
+          <t>2025-11-14 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788077778</t>
+          <t>788086754</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ddelaguilatamani</t>
+          <t>didopracha</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-11 16:05:59</t>
+          <t>2025-11-14 14:50:25</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788077853</t>
+          <t>788086925</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luzcarmen</t>
+          <t>lostres333</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/2.57</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-11 16:43:16</t>
+          <t>2025-11-14 16:49:43</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788077910</t>
+          <t>788086970</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jesusgonzales</t>
+          <t>alex1990</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-11 17:17:27</t>
+          <t>2025-11-14 17:26:18</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788077928</t>
+          <t>788087000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Franklin15</t>
+          <t>icela</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-11 17:34:48</t>
+          <t>2025-11-14 17:41:38</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788077934</t>
+          <t>788087024</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>gavaca5</t>
+          <t>jita1992</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-11 17:36:42</t>
+          <t>2025-11-14 18:03:51</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788077949</t>
+          <t>788087111</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>osito.123</t>
+          <t>Mylongas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/60.00</t>
+          <t>S/0.24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:22</t>
+          <t>2025-11-14 19:27:06</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788077967</t>
+          <t>788087204</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Xxkulerokill</t>
+          <t>mayiii123</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-11 18:02:26</t>
+          <t>2025-11-14 21:14:54</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788077982</t>
+          <t>788087219</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gatito_555</t>
+          <t>Viquita28</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S/0.20</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-11 18:13:09</t>
+          <t>2025-11-14 21:43:33</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788078066</t>
+          <t>788087228</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>40014068</t>
+          <t>Milo32</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.73</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-11 19:29:56</t>
+          <t>2025-11-14 22:00:28</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788078096</t>
+          <t>788087231</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alessia1606</t>
+          <t>joscelo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-11 19:49:05</t>
+          <t>2025-11-14 22:05:04</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788078099</t>
+          <t>788087240</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>daza12</t>
+          <t>chorri</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-11 19:54:35</t>
+          <t>2025-11-14 22:24:36</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788078114</t>
+          <t>788087264</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>cotete0511</t>
+          <t>edvin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-11 20:27:25</t>
+          <t>2025-11-14 23:10:46</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788078150</t>
+          <t>788087294</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>chemapro123</t>
+          <t>Yalobaes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-11 21:20:14</t>
+          <t>2025-11-14 23:57:35</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788078168</t>
+          <t>788087297</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>lochibeto23</t>
+          <t>isabel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-11 22:06:43</t>
+          <t>2025-11-15 00:15:31</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>788078171</t>
+          <t>788087324</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jeffreyarmas30</t>
+          <t>75336221</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-11-11 22:14:15</t>
+          <t>2025-11-15 00:53:19</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>788078186</t>
+          <t>788087330</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jaykoperu</t>
+          <t>magi29</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-11-11 22:39:53</t>
+          <t>2025-11-15 01:12:21</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>788078195</t>
+          <t>788087534</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Julio82</t>
+          <t>Elogio</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-11-11 22:49:10</t>
+          <t>2025-11-15 05:20:32</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>788078210</t>
+          <t>788087741</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>luisvergara</t>
+          <t>Chloe2030</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-11-11 23:13:22</t>
+          <t>2025-11-15 06:40:56</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>788078225</t>
+          <t>788087870</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>postrador</t>
+          <t>Verrospy25</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2200,7 +2200,3991 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-11-11 23:46:51</t>
+          <t>2025-11-15 07:08:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788088491</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>vriixxito</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-11-15 09:03:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788089127</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dante111</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-11-15 10:52:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788089370</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Jbazan97</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-11-15 11:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788089586</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>santossilviafarfanov...</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-11-15 12:15:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788089886</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Luu10</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-11-15 13:21:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788090186</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>marden</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-11-15 15:47:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788090282</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AQUINO19</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-11-15 17:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788090294</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Owensilva</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-11-15 17:10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788090309</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>juan1020</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-11-15 17:41:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788090339</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Jhosselin</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-11-15 18:15:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788090357</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>eden1803</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-11-15 18:24:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788090366</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Joruc</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-11-15 18:46:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788090372</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ciclope23</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.40</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-11-15 18:46:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788090378</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Alonsho2025g</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-11-15 18:55:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788090396</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TERWAL28</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-11-15 19:12:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788090432</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CEDRON</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-11-15 19:53:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788090456</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>johnA69</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/20.60</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:16:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788090459</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>juano12</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:21:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788090465</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Onlyzam10</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.46</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:29:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788090468</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>soyita</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:32:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788090471</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MRM</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:34:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788090483</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>anni927</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:50:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788090486</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TheAnt</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788090489</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>linton</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-11-15 20:55:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788090516</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Miller302</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-11-15 21:20:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788090531</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>geminis1991</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-11-15 21:36:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788090534</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Gabriel19</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-11-15 21:39:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788090552</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>manu.2005</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:29:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788090561</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>chinaqueen</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:53:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788090615</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mch20251181</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-11-16 00:47:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788090618</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>zoilis</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-11-16 01:01:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788090651</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ReXxDs28</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-11-16 02:54:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788090837</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sexi</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-11-16 06:33:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788090858</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dhark-lee</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-11-16 06:41:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788090888</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cortegana</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-11-16 06:52:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788091059</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>927832452</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-11-16 07:35:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788091239</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>231456</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-11-16 08:25:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788091281</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>quincho17</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-11-16 08:44:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788091401</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dignacruz1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-11-16 09:14:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788091455</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dorca123</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-11-16 09:35:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788091737</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>miguel1983</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-11-16 11:07:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788091797</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ancajima</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-11-16 11:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788091818</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jesusaular</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-11-16 11:34:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788092046</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>miguel1948</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-11-16 13:03:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788092106</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>nanoneyra</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-11-16 13:36:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788092220</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>arnaldo123</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-11-16 14:39:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788092235</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PaoMC87</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-11-16 14:55:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788092415</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Danielsaucedo_2004</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-11-16 16:52:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788092433</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>emerson2006</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-11-16 17:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788092529</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>dianacast31</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-11-16 19:02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788092568</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Creyescuba</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-11-16 20:13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788092577</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>dante76</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-11-16 20:20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788092601</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>chotamaca</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-11-16 21:10:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788092622</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>JairIsraelMB</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-11-16 21:51:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788092637</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>jonatan1236</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-11-16 22:27:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788092670</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>saritadelaguilaruiz4...</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-11-16 23:55:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788092673</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Russ</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.90</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788093270</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Elchacatexas</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.27</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-11-17 07:33:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788093645</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>yakori</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-11-17 08:38:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788094548</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Feprueba</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-11-17 10:54:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>788094656</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MnlAraujo</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-11-17 11:09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>788094866</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ricrapaganandres</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-11-17 11:38:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>788095193</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Alejandr069</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2025-11-17 12:24:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>788095481</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>enzo1006</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S/0.04</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2025-11-17 13:22:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>788095637</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>libra87</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2025-11-17 14:37:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>788095658</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Nohelia</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2025-11-17 14:52:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>788095703</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>alfredito12</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2025-11-17 15:23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>788095733</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>yeison3030</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2025-11-17 15:46:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>788095799</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Grinchhh</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2025-11-17 16:43:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>788095859</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>cordova19937</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2025-11-17 17:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>788095868</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>canzer1230Z</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2025-11-17 17:22:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>788095883</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>gusta</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2025-11-17 17:24:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>788095898</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>luisjoel</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2025-11-17 17:36:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>788095910</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Harold18</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2025-11-17 18:12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>788095928</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Jntzvl1907</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S/0.08</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2025-11-17 18:32:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>788095955</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>JHUANECS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2025-11-17 19:34:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>788095967</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>sofidi</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2025-11-17 19:51:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>788095979</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Waldir2p</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2025-11-17 20:15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>788095994</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Dskota28</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2025-11-17 21:04:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>788096000</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>waldir7</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2025-11-17 21:13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>788096018</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>THEPOWER1986</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2025-11-17 21:47:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>788096036</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>chavitoavm</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2025-11-17 22:19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>788096048</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Joz99</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2025-11-17 23:03:17</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788096099</t>
+          <t>788099720</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kenyo</t>
+          <t>Rosy30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-18 00:56:48</t>
+          <t>2025-11-19 00:03:56</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788096114</t>
+          <t>788099735</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trave</t>
+          <t>Zt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-18 01:20:37</t>
+          <t>2025-11-19 00:46:18</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788096594</t>
+          <t>788099765</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Naruto78</t>
+          <t>nestor10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-18 07:02:45</t>
+          <t>2025-11-19 01:35:07</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788096852</t>
+          <t>788099768</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>elias50</t>
+          <t>Pieer0405</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-18 07:49:52</t>
+          <t>2025-11-19 01:35:35</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788097911</t>
+          <t>788099771</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FREDDYQS</t>
+          <t>Abraham7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-18 09:52:42</t>
+          <t>2025-11-19 01:36:54</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788097959</t>
+          <t>788099843</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>chambipandia</t>
+          <t>12345fidel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-18 09:56:48</t>
+          <t>2025-11-19 03:26:47</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788098106</t>
+          <t>788099855</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GERSSONPAILUNO</t>
+          <t>Frankie0704</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-18 10:13:08</t>
+          <t>2025-11-19 03:33:10</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788098187</t>
+          <t>788099879</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salinas10</t>
+          <t>ganador28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-18 10:28:20</t>
+          <t>2025-11-19 04:00:44</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788098313</t>
+          <t>788100035</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>aston</t>
+          <t>wilsonRiosSangama</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-18 10:48:30</t>
+          <t>2025-11-19 05:16:52</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788098703</t>
+          <t>788100428</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gladys1</t>
+          <t>Ventu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-18 11:56:43</t>
+          <t>2025-11-19 06:37:32</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788098805</t>
+          <t>788100917</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ratma</t>
+          <t>luislucas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-18 12:24:50</t>
+          <t>2025-11-19 07:48:59</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788098937</t>
+          <t>788101463</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SERAPIO</t>
+          <t>Chato1995</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-18 13:00:53</t>
+          <t>2025-11-19 09:12:01</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788099129</t>
+          <t>788102198</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lucano08</t>
+          <t>Gracee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-18 14:12:40</t>
+          <t>2025-11-19 11:28:30</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788099153</t>
+          <t>788102372</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>guille2405</t>
+          <t>46804905</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-18 14:24:30</t>
+          <t>2025-11-19 11:58:47</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788099189</t>
+          <t>788102378</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>luceroagui1995</t>
+          <t>dereteo12345</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-18 14:37:27</t>
+          <t>2025-11-19 11:59:21</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788099273</t>
+          <t>788102402</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>40806579</t>
+          <t>yuniormayer1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-18 15:28:03</t>
+          <t>2025-11-19 12:02:48</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788099303</t>
+          <t>788102465</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>junior2817</t>
+          <t>dyancoa1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S/0.02</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-18 15:40:02</t>
+          <t>2025-11-19 12:13:20</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788099348</t>
+          <t>788102657</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>76040352</t>
+          <t>ochoita</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-18 16:02:17</t>
+          <t>2025-11-19 12:47:26</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788099396</t>
+          <t>788103035</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rafael1607</t>
+          <t>cesar.ernesto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-18 16:39:56</t>
+          <t>2025-11-19 15:17:17</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788099447</t>
+          <t>788103164</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FRANCISCOCR10</t>
+          <t>elvis666</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-18 17:35:50</t>
+          <t>2025-11-19 16:28:49</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788099462</t>
+          <t>788103236</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rvao</t>
+          <t>Chaka</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-18 17:53:26</t>
+          <t>2025-11-19 17:06:25</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788099531</t>
+          <t>788103350</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>tukchero</t>
+          <t>Brahayam7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-18 19:06:09</t>
+          <t>2025-11-19 18:44:24</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788099621</t>
+          <t>788103371</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milita.85</t>
+          <t>Rotin56</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-18 21:28:45</t>
+          <t>2025-11-19 19:05:02</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788099624</t>
+          <t>788103380</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Javier33</t>
+          <t>yusme</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-18 21:35:27</t>
+          <t>2025-11-19 19:14:54</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788099699</t>
+          <t>788103383</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ana18</t>
+          <t>Loca25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-18 23:21:40</t>
+          <t>2025-11-19 19:18:44</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788099702</t>
+          <t>788103386</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jord7</t>
+          <t>cjf25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-18 23:25:04</t>
+          <t>2025-11-19 19:19:30</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788099708</t>
+          <t>788103392</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jhoelcp19j</t>
+          <t>mathiu31052011</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,151 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-18 23:44:57</t>
+          <t>2025-11-19 19:28:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788103431</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sti</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-11-19 20:19:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788103452</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>palta</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-11-19 20:56:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788103515</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>hectorlopez</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-11-19 23:11:10</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788103599</t>
+          <t>788105852</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gianfarc</t>
+          <t>choquito</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-20 03:18:23</t>
+          <t>2025-11-21 01:22:03</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788104124</t>
+          <t>788106866</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>poolilla24</t>
+          <t>operacionestest</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-20 08:06:49</t>
+          <t>2025-11-21 10:45:57</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788105651</t>
+          <t>788107580</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anthony20</t>
+          <t>villano30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-20 18:54:39</t>
+          <t>2025-11-21 14:58:48</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788105660</t>
+          <t>788107616</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cristhian2</t>
+          <t>luislanz28146</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-20 19:04:45</t>
+          <t>2025-11-21 15:31:50</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788105729</t>
+          <t>788107631</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Rogger10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-20 20:04:11</t>
+          <t>2025-11-21 15:39:03</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788105732</t>
+          <t>788107751</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>zona4087</t>
+          <t>jailer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-20 20:11:02</t>
+          <t>2025-11-21 17:06:03</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788105762</t>
+          <t>788107913</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ROMERPEREZ06</t>
+          <t>guedez123</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-20 20:45:10</t>
+          <t>2025-11-21 19:38:31</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788105765</t>
+          <t>788107997</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eliceo08</t>
+          <t>valverde123</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-20 20:45:40</t>
+          <t>2025-11-21 21:24:24</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788105798</t>
+          <t>788108078</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>raulriveravasquez777</t>
+          <t>apeiron</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-20 22:32:24</t>
+          <t>2025-11-22 00:43:07</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788105810</t>
+          <t>788108912</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ronyelu</t>
+          <t>MXNITO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-20 22:58:37</t>
+          <t>2025-11-22 09:32:45</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788105816</t>
+          <t>788109848</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nader</t>
+          <t>Kitty2199</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S/700.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1000,7 +1000,343 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-20 23:14:41</t>
+          <t>2025-11-22 14:02:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>788110178</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>eduardotello123</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2025-11-22 18:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>788111102</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>rafaelmontilla56</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2025-11-23 07:41:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>788111312</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>marinsequera22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2025-11-23 09:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>788111933</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>tommymot</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2025-11-23 13:38:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>788112080</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Liset123</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2025-11-23 15:19:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>788112086</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>walter1998</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2025-11-23 15:25:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>788112425</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sanchezarandaeveliz</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2025-11-23 23:06:22</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788105852</t>
+          <t>788112536</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>choquito</t>
+          <t>Edukj2099</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-21 01:22:03</t>
+          <t>2025-11-24 03:00:19</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788106866</t>
+          <t>788113145</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>operacionestest</t>
+          <t>abanto</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-21 10:45:57</t>
+          <t>2025-11-24 09:45:29</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788107580</t>
+          <t>788113394</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>villano30</t>
+          <t>Alciracasma</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-21 14:58:48</t>
+          <t>2025-11-24 11:16:01</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788107616</t>
+          <t>788113424</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>luislanz28146</t>
+          <t>Dey1234</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S/0.60</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-21 15:31:50</t>
+          <t>2025-11-24 11:22:41</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788107631</t>
+          <t>788113427</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rogger10</t>
+          <t>montoro21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-21 15:39:03</t>
+          <t>2025-11-24 11:23:06</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788107751</t>
+          <t>788113514</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jailer</t>
+          <t>aldomi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-21 17:06:03</t>
+          <t>2025-11-24 11:59:11</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788107913</t>
+          <t>788113790</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>guedez123</t>
+          <t>ulde</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-21 19:38:31</t>
+          <t>2025-11-24 14:04:39</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788107997</t>
+          <t>788113814</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>valverde123</t>
+          <t>Davr</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-21 21:24:24</t>
+          <t>2025-11-24 14:14:40</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788108078</t>
+          <t>788113838</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>apeiron</t>
+          <t>85152134</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-22 00:43:07</t>
+          <t>2025-11-24 14:26:53</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788108912</t>
+          <t>788113874</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MXNITO</t>
+          <t>ANNIA1520</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-22 09:32:45</t>
+          <t>2025-11-24 14:44:23</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788109848</t>
+          <t>788113925</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kitty2199</t>
+          <t>diegoraa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-22 14:02:31</t>
+          <t>2025-11-24 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788110178</t>
+          <t>788113940</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eduardotello123</t>
+          <t>edwina</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-22 18:19:52</t>
+          <t>2025-11-24 15:15:02</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788111102</t>
+          <t>788113943</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rafaelmontilla56</t>
+          <t>Gabrielon123321</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-23 07:41:40</t>
+          <t>2025-11-24 15:21:41</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788111312</t>
+          <t>788114006</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>marinsequera22</t>
+          <t>unica66</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-23 09:07:57</t>
+          <t>2025-11-24 15:59:39</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788111933</t>
+          <t>788114024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>tommymot</t>
+          <t>cremita28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-23 13:38:00</t>
+          <t>2025-11-24 16:09:12</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788112080</t>
+          <t>788114114</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Liset123</t>
+          <t>Duber2907</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Habilitado</t>
+          <t>Congelado</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-23 15:19:28</t>
+          <t>2025-11-24 17:01:51</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788112086</t>
+          <t>788114135</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>walter1998</t>
+          <t>Angie2919</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-23 15:25:33</t>
+          <t>2025-11-24 17:06:26</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788112425</t>
+          <t>788114231</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sanchezarandaeveliz</t>
+          <t>jhonjara90</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,631 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-23 23:06:22</t>
+          <t>2025-11-24 18:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>788114234</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>joszp</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2025-11-24 18:21:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>788114255</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>moro</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2025-11-24 18:30:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>788114294</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Likito</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2025-11-24 19:09:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>788114297</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Karlu</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2025-11-24 19:10:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>788114330</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>elsa2411</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2025-11-24 19:41:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>788114342</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>freddy288</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2025-11-24 19:59:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>788114351</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Miguel2006</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2025-11-24 20:15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>788114369</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Diefer10</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-11-24 20:40:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>788114384</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>leitop</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-11-24 21:02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788114396</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ericson85</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-11-24 21:09:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788114417</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jhonarnasvela</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-11-24 21:48:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788114459</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-11-24 22:26:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788114519</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Alha</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-11-24 23:45:14</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788112536</t>
+          <t>788114621</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Edukj2099</t>
+          <t>Luis12391</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-24 03:00:19</t>
+          <t>2025-11-25 03:46:53</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788113145</t>
+          <t>788115173</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>abanto</t>
+          <t>jorgezapata1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-24 09:45:29</t>
+          <t>2025-11-25 08:47:24</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788113394</t>
+          <t>788115179</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alciracasma</t>
+          <t>Jhan5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-24 11:16:01</t>
+          <t>2025-11-25 08:49:37</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788113424</t>
+          <t>788115197</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dey1234</t>
+          <t>Juaneco87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-24 11:22:41</t>
+          <t>2025-11-25 08:55:00</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788113427</t>
+          <t>788115227</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>montoro21</t>
+          <t>Carmona1994</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-24 11:23:06</t>
+          <t>2025-11-25 09:03:38</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788113514</t>
+          <t>788115566</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>aldomi</t>
+          <t>jackson6gmontenegro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-24 11:59:11</t>
+          <t>2025-11-25 10:58:51</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788113790</t>
+          <t>788115761</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ulde</t>
+          <t>gaturroblack</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-24 14:04:39</t>
+          <t>2025-11-25 11:38:13</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788113814</t>
+          <t>788115824</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Davr</t>
+          <t>franciscojavierbenit...</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/20.00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-24 14:14:40</t>
+          <t>2025-11-25 11:57:25</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788113838</t>
+          <t>788115833</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>85152134</t>
+          <t>Patty28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-24 14:26:53</t>
+          <t>2025-11-25 11:59:08</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788113874</t>
+          <t>788115854</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANNIA1520</t>
+          <t>yonjulca</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-24 14:44:23</t>
+          <t>2025-11-25 12:04:27</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788113925</t>
+          <t>788115869</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>diegoraa</t>
+          <t>briceno25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-24 15:10:30</t>
+          <t>2025-11-25 12:08:03</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788113940</t>
+          <t>788116001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>edwina</t>
+          <t>VARGAS228</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S/0.02</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-24 15:15:02</t>
+          <t>2025-11-25 12:41:00</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788113943</t>
+          <t>788116013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gabrielon123321</t>
+          <t>Leivakass</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-24 15:21:41</t>
+          <t>2025-11-25 12:42:30</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788114006</t>
+          <t>788116046</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unica66</t>
+          <t>reynajc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-24 15:59:39</t>
+          <t>2025-11-25 12:51:46</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788114024</t>
+          <t>788116100</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cremita28</t>
+          <t>Lupenao</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-24 16:09:12</t>
+          <t>2025-11-25 13:08:18</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788114114</t>
+          <t>788116193</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Duber2907</t>
+          <t>DIAZ14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Congelado</t>
+          <t>Habilitado</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-24 17:01:51</t>
+          <t>2025-11-25 13:28:53</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788114135</t>
+          <t>788116205</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Angie2919</t>
+          <t>ayala2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-24 17:06:26</t>
+          <t>2025-11-25 13:34:29</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788114231</t>
+          <t>788116241</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jhonjara90</t>
+          <t>76557600</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-24 18:20:03</t>
+          <t>2025-11-25 13:42:44</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788114234</t>
+          <t>788116247</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>joszp</t>
+          <t>JUAN2004</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-24 18:21:56</t>
+          <t>2025-11-25 13:43:35</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788114255</t>
+          <t>788116433</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>moro</t>
+          <t>josue97</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-24 18:30:29</t>
+          <t>2025-11-25 14:47:00</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788114294</t>
+          <t>788116466</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Likito</t>
+          <t>aguicesar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-24 19:09:15</t>
+          <t>2025-11-25 14:57:05</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788114297</t>
+          <t>788116517</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Karlu</t>
+          <t>leonel2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-24 19:10:49</t>
+          <t>2025-11-25 15:21:04</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788114330</t>
+          <t>788116526</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>elsa2411</t>
+          <t>jose944</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-24 19:41:10</t>
+          <t>2025-11-25 15:25:32</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788114342</t>
+          <t>788116682</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>freddy288</t>
+          <t>maylincango</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-24 19:59:16</t>
+          <t>2025-11-25 16:51:16</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788114351</t>
+          <t>788116706</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miguel2006</t>
+          <t>carloman123</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-24 20:15:05</t>
+          <t>2025-11-25 17:07:21</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788114369</t>
+          <t>788116781</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Diefer10</t>
+          <t>johnnypl</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-24 20:40:15</t>
+          <t>2025-11-25 17:58:04</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788114384</t>
+          <t>788116838</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>leitop</t>
+          <t>leninolin78</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-24 21:02:45</t>
+          <t>2025-11-25 18:37:09</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788114396</t>
+          <t>788116868</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ericson85</t>
+          <t>cbernilla</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-24 21:09:09</t>
+          <t>2025-11-25 19:07:10</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788114417</t>
+          <t>788116883</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jhonarnasvela</t>
+          <t>Matthewvalto20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-24 21:48:46</t>
+          <t>2025-11-25 19:19:35</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788114459</t>
+          <t>788116967</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>ortechocristian</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-24 22:26:29</t>
+          <t>2025-11-25 21:22:02</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788114519</t>
+          <t>788116970</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alha</t>
+          <t>balack1993</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,391 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-24 23:45:14</t>
+          <t>2025-11-25 21:29:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788116982</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Abdiel</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/15.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-11-25 21:51:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788117015</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mila060822</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-11-25 22:36:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788117027</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jhas160482</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-11-25 22:47:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788117033</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Yesi20</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-11-25 23:01:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788117039</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>80225183</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-11-25 23:17:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788117045</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>katherine</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-11-25 23:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788117051</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dragon</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-11-25 23:42:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788117054</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GkjL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-11-25 23:56:22</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788114621</t>
+          <t>788117057</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luis12391</t>
+          <t>Alfo2411</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-25 03:46:53</t>
+          <t>2025-11-26 00:07:27</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788115173</t>
+          <t>788117060</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jorgezapata1</t>
+          <t>vicffz</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-25 08:47:24</t>
+          <t>2025-11-26 00:07:28</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788115179</t>
+          <t>788117099</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jhan5</t>
+          <t>Ivan_bances21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-25 08:49:37</t>
+          <t>2025-11-26 01:10:15</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788115197</t>
+          <t>788117102</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Juaneco87</t>
+          <t>44758619</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-25 08:55:00</t>
+          <t>2025-11-26 01:15:32</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788115227</t>
+          <t>788117123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carmona1994</t>
+          <t>43621131</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-25 09:03:38</t>
+          <t>2025-11-26 02:13:21</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788115566</t>
+          <t>788117129</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jackson6gmontenegro</t>
+          <t>Mario597</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-25 10:58:51</t>
+          <t>2025-11-26 02:38:25</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788115761</t>
+          <t>788117243</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gaturroblack</t>
+          <t>jovetorresl</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-25 11:38:13</t>
+          <t>2025-11-26 05:04:38</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788115824</t>
+          <t>788117309</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>franciscojavierbenit...</t>
+          <t>75961118</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S/20.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-25 11:57:25</t>
+          <t>2025-11-26 05:56:45</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788115833</t>
+          <t>788117495</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patty28</t>
+          <t>Darvi15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-25 11:59:08</t>
+          <t>2025-11-26 07:21:12</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788115854</t>
+          <t>788117672</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yonjulca</t>
+          <t>LuisMi040802</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-25 12:04:27</t>
+          <t>2025-11-26 08:35:09</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788115869</t>
+          <t>788117759</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>briceno25</t>
+          <t>dominguezsanchezhenr...</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-25 12:08:03</t>
+          <t>2025-11-26 09:00:57</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788116001</t>
+          <t>788117795</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VARGAS228</t>
+          <t>Lauracgz96</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-25 12:41:00</t>
+          <t>2025-11-26 09:12:40</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788116013</t>
+          <t>788118239</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leivakass</t>
+          <t>Sewis</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-25 12:42:30</t>
+          <t>2025-11-26 11:30:31</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788116046</t>
+          <t>788118398</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>reynajc</t>
+          <t>florian71</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-25 12:51:46</t>
+          <t>2025-11-26 12:30:30</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788116100</t>
+          <t>788118761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lupenao</t>
+          <t>diazraul123</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-25 13:08:18</t>
+          <t>2025-11-26 14:11:03</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788116193</t>
+          <t>788118830</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIAZ14</t>
+          <t>Matoncito455</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-25 13:28:53</t>
+          <t>2025-11-26 14:38:29</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788116205</t>
+          <t>788118842</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ayala2025</t>
+          <t>pantaleon17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-25 13:34:29</t>
+          <t>2025-11-26 14:44:13</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788116241</t>
+          <t>788118914</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>76557600</t>
+          <t>Cat23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-25 13:42:44</t>
+          <t>2025-11-26 15:03:09</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788116247</t>
+          <t>788118920</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JUAN2004</t>
+          <t>Axcel06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-25 13:43:35</t>
+          <t>2025-11-26 15:03:30</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788116433</t>
+          <t>788119034</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>josue97</t>
+          <t>anakely</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-25 14:47:00</t>
+          <t>2025-11-26 15:33:24</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788116466</t>
+          <t>788119121</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>aguicesar</t>
+          <t>katiana</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-25 14:57:05</t>
+          <t>2025-11-26 16:13:56</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788116517</t>
+          <t>788119190</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>leonel2025</t>
+          <t>Dulce391</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-25 15:21:04</t>
+          <t>2025-11-26 16:50:37</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788116526</t>
+          <t>788119250</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jose944</t>
+          <t>yasir777</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-25 15:25:32</t>
+          <t>2025-11-26 17:26:25</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788116682</t>
+          <t>788119268</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>maylincango</t>
+          <t>alber_andre</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-25 16:51:16</t>
+          <t>2025-11-26 17:35:25</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788116706</t>
+          <t>788119271</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>carloman123</t>
+          <t>prestown08</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-25 17:07:21</t>
+          <t>2025-11-26 17:37:18</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788116781</t>
+          <t>788119301</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>johnnypl</t>
+          <t>Kripador15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-25 17:58:04</t>
+          <t>2025-11-26 17:54:13</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788116838</t>
+          <t>788119331</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>leninolin78</t>
+          <t>71754095</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-25 18:37:09</t>
+          <t>2025-11-26 18:09:38</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788116868</t>
+          <t>788119337</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>cbernilla</t>
+          <t>Babygomita</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-25 19:07:10</t>
+          <t>2025-11-26 18:12:14</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788116883</t>
+          <t>788119343</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Matthewvalto20</t>
+          <t>juankapibe123</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-25 19:19:35</t>
+          <t>2025-11-26 18:14:46</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788116967</t>
+          <t>788119379</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ortechocristian</t>
+          <t>Ozken</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-25 21:22:02</t>
+          <t>2025-11-26 18:42:16</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788116970</t>
+          <t>788119487</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>balack1993</t>
+          <t>jhonathanseven22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-25 21:29:37</t>
+          <t>2025-11-26 20:49:30</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>788116982</t>
+          <t>788119538</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Abdiel</t>
+          <t>Bherlin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>S/15.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-11-25 21:51:05</t>
+          <t>2025-11-26 22:12:23</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>788117015</t>
+          <t>788119547</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mila060822</t>
+          <t>Zen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-11-25 22:36:51</t>
+          <t>2025-11-26 22:29:56</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>788117027</t>
+          <t>788119553</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jhas160482</t>
+          <t>Piloacacio</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-11-25 22:47:27</t>
+          <t>2025-11-26 22:34:18</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>788117033</t>
+          <t>788119559</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yesi20</t>
+          <t>Irenefg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/2,500.55</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-11-25 23:01:02</t>
+          <t>2025-11-26 22:54:16</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>788117039</t>
+          <t>788119562</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>80225183</t>
+          <t>Otorongo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-11-25 23:17:28</t>
+          <t>2025-11-26 22:55:44</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>788117045</t>
+          <t>788119580</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>katherine</t>
+          <t>luchotimbero</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/30.00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2025-11-25 23:33:50</t>
+          <t>2025-11-26 23:39:04</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>788117051</t>
+          <t>788119592</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>JesusFarro1998</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2296,55 +2296,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-11-25 23:42:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>788117054</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>GkjL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2025-11-25 23:56:22</t>
+          <t>2025-11-26 23:58:59</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788117057</t>
+          <t>788119598</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alfo2411</t>
+          <t>mily2312</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-26 00:07:27</t>
+          <t>2025-11-27 00:06:24</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788117060</t>
+          <t>788119616</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vicffz</t>
+          <t>Chamuco</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-26 00:07:28</t>
+          <t>2025-11-27 00:39:45</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788117099</t>
+          <t>788119838</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ivan_bances21</t>
+          <t>horson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-26 01:10:15</t>
+          <t>2025-11-27 05:05:12</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788117102</t>
+          <t>788119925</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>44758619</t>
+          <t>43948252</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/37.60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-26 01:15:32</t>
+          <t>2025-11-27 05:58:33</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788117123</t>
+          <t>788120039</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43621131</t>
+          <t>weboncin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-26 02:13:21</t>
+          <t>2025-11-27 06:56:04</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788117129</t>
+          <t>788120054</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mario597</t>
+          <t>AngelMiraval</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S/0.03</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-26 02:38:25</t>
+          <t>2025-11-27 07:08:16</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788117243</t>
+          <t>788120069</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jovetorresl</t>
+          <t>josr2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/44.60</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-26 05:04:38</t>
+          <t>2025-11-27 07:20:18</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788117309</t>
+          <t>788120132</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>75961118</t>
+          <t>Marian</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-26 05:56:45</t>
+          <t>2025-11-27 07:45:14</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788117495</t>
+          <t>788120276</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Darvi15</t>
+          <t>Xato1995</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-26 07:21:12</t>
+          <t>2025-11-27 08:23:10</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788117672</t>
+          <t>788120285</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LuisMi040802</t>
+          <t>wilmedina</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-26 08:35:09</t>
+          <t>2025-11-27 08:25:25</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788117759</t>
+          <t>788120378</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dominguezsanchezhenr...</t>
+          <t>fernandoM01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-26 09:00:57</t>
+          <t>2025-11-27 08:54:39</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788117795</t>
+          <t>788120726</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lauracgz96</t>
+          <t>vitocho89</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-26 09:12:40</t>
+          <t>2025-11-27 10:51:44</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788118239</t>
+          <t>788120762</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sewis</t>
+          <t>Juniormaza</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-26 11:30:31</t>
+          <t>2025-11-27 11:02:39</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788118398</t>
+          <t>788120783</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>florian71</t>
+          <t>IRAZABAL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-26 12:30:30</t>
+          <t>2025-11-27 11:09:02</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788118761</t>
+          <t>788120807</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>diazraul123</t>
+          <t>XOLGT2011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-26 14:11:03</t>
+          <t>2025-11-27 11:16:09</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788118830</t>
+          <t>788120825</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Matoncito455</t>
+          <t>hectorpanaifo9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-26 14:38:29</t>
+          <t>2025-11-27 11:22:50</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788118842</t>
+          <t>788121485</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pantaleon17</t>
+          <t>elsinnombre</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-26 14:44:13</t>
+          <t>2025-11-27 15:28:46</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788118914</t>
+          <t>788121569</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cat23</t>
+          <t>Arteaga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-26 15:03:09</t>
+          <t>2025-11-27 16:04:07</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788118920</t>
+          <t>788121578</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Axcel06</t>
+          <t>jared1995</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-26 15:03:30</t>
+          <t>2025-11-27 16:05:33</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788119034</t>
+          <t>788121611</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>anakely</t>
+          <t>32923356</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S/0.05</t>
+          <t>S/8.00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-26 15:33:24</t>
+          <t>2025-11-27 16:30:25</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788119121</t>
+          <t>788121614</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>katiana</t>
+          <t>moisesric</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-26 16:13:56</t>
+          <t>2025-11-27 16:30:55</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788119190</t>
+          <t>788121653</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dulce391</t>
+          <t>martin35</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-26 16:50:37</t>
+          <t>2025-11-27 16:51:21</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788119250</t>
+          <t>788121728</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yasir777</t>
+          <t>Luis2007</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/0.08</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-26 17:26:25</t>
+          <t>2025-11-27 17:42:33</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788119268</t>
+          <t>788121776</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>alber_andre</t>
+          <t>cristhiang05</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-26 17:35:25</t>
+          <t>2025-11-27 18:01:42</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788119271</t>
+          <t>788121803</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>prestown08</t>
+          <t>Erwin96</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-26 17:37:18</t>
+          <t>2025-11-27 18:16:28</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788119301</t>
+          <t>788121884</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kripador15</t>
+          <t>Kev</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-26 17:54:13</t>
+          <t>2025-11-27 19:42:03</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788119331</t>
+          <t>788121941</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>71754095</t>
+          <t>wilitec</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-26 18:09:38</t>
+          <t>2025-11-27 20:46:27</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788119337</t>
+          <t>788121947</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Babygomita</t>
+          <t>love</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-26 18:12:14</t>
+          <t>2025-11-27 21:18:45</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788119343</t>
+          <t>788121950</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>juankapibe123</t>
+          <t>Eveliap</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-26 18:14:46</t>
+          <t>2025-11-27 21:20:56</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788119379</t>
+          <t>788121980</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ozken</t>
+          <t>31520959</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-26 18:42:16</t>
+          <t>2025-11-27 22:34:25</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788119487</t>
+          <t>788122004</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jhonathanseven22</t>
+          <t>Jsema</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/80.01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1960,343 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-26 20:49:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>788119538</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Bherlin</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2025-11-26 22:12:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>788119547</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Zen</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2025-11-26 22:29:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>788119553</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Piloacacio</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2025-11-26 22:34:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>788119559</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Irenefg</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S/2,500.55</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2025-11-26 22:54:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>788119562</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Otorongo</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2025-11-26 22:55:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>788119580</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>luchotimbero</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S/30.00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2025-11-26 23:39:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>788119592</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>JesusFarro1998</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2025-11-26 23:58:59</t>
+          <t>2025-11-27 23:01:22</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788119598</t>
+          <t>788122088</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mily2312</t>
+          <t>mar0401abdiel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-27 00:06:24</t>
+          <t>2025-11-28 00:47:38</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788119616</t>
+          <t>788122793</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chamuco</t>
+          <t>rios2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-11-27 00:39:45</t>
+          <t>2025-11-28 09:20:57</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788119838</t>
+          <t>788122937</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>horson</t>
+          <t>sullon12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S/0.27</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-11-27 05:05:12</t>
+          <t>2025-11-28 10:00:55</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788119925</t>
+          <t>788122955</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43948252</t>
+          <t>Malena299</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S/37.60</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-11-27 05:58:33</t>
+          <t>2025-11-28 10:03:16</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788120039</t>
+          <t>788122958</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>weboncin</t>
+          <t>sullon123456789</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-11-27 06:56:04</t>
+          <t>2025-11-28 10:03:53</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788120054</t>
+          <t>788123069</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AngelMiraval</t>
+          <t>ROBRAM06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-11-27 07:08:16</t>
+          <t>2025-11-28 10:22:18</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788120069</t>
+          <t>788123174</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>josr2025</t>
+          <t>negracho90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/44.60</t>
+          <t>S/0.13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-11-27 07:20:18</t>
+          <t>2025-11-28 10:45:17</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788120132</t>
+          <t>788123201</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>kevinzavala22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-11-27 07:45:14</t>
+          <t>2025-11-28 10:50:17</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788120276</t>
+          <t>788123429</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xato1995</t>
+          <t>elucha</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-27 08:23:10</t>
+          <t>2025-11-28 11:47:18</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788120285</t>
+          <t>788123510</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wilmedina</t>
+          <t>galantix2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-11-27 08:25:25</t>
+          <t>2025-11-28 12:14:29</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788120378</t>
+          <t>788123558</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fernandoM01</t>
+          <t>Carlosjhon</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-27 08:54:39</t>
+          <t>2025-11-28 12:26:55</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788120726</t>
+          <t>788123642</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>vitocho89</t>
+          <t>negrita</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-11-27 10:51:44</t>
+          <t>2025-11-28 12:49:21</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788120762</t>
+          <t>788123699</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Juniormaza</t>
+          <t>ByNizand</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-27 11:02:39</t>
+          <t>2025-11-28 13:02:42</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788120783</t>
+          <t>788123858</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IRAZABAL</t>
+          <t>DiegoRomanAdriano</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-27 11:09:02</t>
+          <t>2025-11-28 14:03:24</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788120807</t>
+          <t>788124017</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>XOLGT2011</t>
+          <t>Negroo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.41</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-27 11:16:09</t>
+          <t>2025-11-28 15:11:43</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788120825</t>
+          <t>788124080</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hectorpanaifo9</t>
+          <t>19christian96</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-27 11:22:50</t>
+          <t>2025-11-28 15:41:47</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788121485</t>
+          <t>788124083</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>elsinnombre</t>
+          <t>joelitoelunico</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-27 15:28:46</t>
+          <t>2025-11-28 15:42:09</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788121569</t>
+          <t>788124122</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arteaga</t>
+          <t>jorgedavid</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-27 16:04:07</t>
+          <t>2025-11-28 16:03:27</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788121578</t>
+          <t>788124140</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jared1995</t>
+          <t>salvadorramirezcumap...</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-27 16:05:33</t>
+          <t>2025-11-28 16:14:59</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788121611</t>
+          <t>788124176</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>32923356</t>
+          <t>Rhapzor23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S/8.00</t>
+          <t>S/21.03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-27 16:30:25</t>
+          <t>2025-11-28 16:25:02</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788121614</t>
+          <t>788124179</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>moisesric</t>
+          <t>Elvis_21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-27 16:30:55</t>
+          <t>2025-11-28 16:30:51</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788121653</t>
+          <t>788124218</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>martin35</t>
+          <t>Magbis1307</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-27 16:51:21</t>
+          <t>2025-11-28 16:56:24</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788121728</t>
+          <t>788124263</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Luis2007</t>
+          <t>chaverolazaro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-27 17:42:33</t>
+          <t>2025-11-28 17:16:17</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788121776</t>
+          <t>788124314</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cristhiang05</t>
+          <t>JEGC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-27 18:01:42</t>
+          <t>2025-11-28 17:41:01</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788121803</t>
+          <t>788124341</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Erwin96</t>
+          <t>omar1997</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-27 18:16:28</t>
+          <t>2025-11-28 17:57:01</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788121884</t>
+          <t>788124410</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kev</t>
+          <t>Rumiche</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-27 19:42:03</t>
+          <t>2025-11-28 18:42:05</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788121941</t>
+          <t>788124485</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wilitec</t>
+          <t>Rossy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-27 20:46:27</t>
+          <t>2025-11-28 20:02:01</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788121947</t>
+          <t>788124521</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>Jhonwar2021</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-27 21:18:45</t>
+          <t>2025-11-28 20:31:14</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788121950</t>
+          <t>788124539</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eveliap</t>
+          <t>74424495</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-27 21:20:56</t>
+          <t>2025-11-28 20:56:32</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788121980</t>
+          <t>788124566</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>31520959</t>
+          <t>frisancho09</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-27 22:34:25</t>
+          <t>2025-11-28 21:11:30</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788122004</t>
+          <t>788124572</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jsema</t>
+          <t>jackymendoza</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S/80.01</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1960,7 +1960,3271 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-27 23:01:22</t>
+          <t>2025-11-28 21:31:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788124623</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dani22</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-11-28 22:42:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788124635</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>gato133</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-11-28 22:59:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788124638</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>drupiboys1391</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-11-28 23:04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788124758</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>theblack</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-11-29 03:31:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788125052</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jose_villa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-11-29 06:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788125064</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Spencer1977</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.47</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-11-29 06:41:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788125112</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Erickz1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-11-29 07:03:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788125418</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>estradaaccel</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-11-29 08:34:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788125628</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BENA0205</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-11-29 09:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788125682</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>paii18.18</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-11-29 09:39:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788125847</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>flor22</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-11-29 10:44:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788125886</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>santiagoacosta123</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-11-29 10:54:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788125901</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>delia</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-11-29 10:56:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788126207</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MARCOSantonio35</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-11-29 12:40:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788126255</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Eulogio</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-11-29 12:55:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788126336</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Patrick26</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-11-29 13:26:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788126381</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Roca2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-11-29 13:42:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788126393</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>pinchi123</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-11-29 13:45:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788126447</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lehoman</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-11-29 14:10:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788126531</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Carloscast50</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-11-29 14:47:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788126534</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Angelo11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-11-29 14:48:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788126540</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jordyct</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.11</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-11-29 14:50:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788126591</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>roman18</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-11-29 15:14:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788126603</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Angel272828</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-11-29 15:21:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788126633</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>eliel22</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-11-29 15:40:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788126660</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ingameza123</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-11-29 15:45:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788126675</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>tuantoni</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-11-29 15:50:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788126702</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>edson1998</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-11-29 16:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788126723</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Yeeiler</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-11-29 16:11:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788126726</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>leonard.1415</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-11-29 16:12:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788126765</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>JORGESALAS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-11-29 16:33:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788126786</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>joseroma27</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-11-29 16:42:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788126846</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Manuel..Gamer</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:10:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788126870</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>wildersantos09</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:21:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788126918</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>javierarias28</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:44:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788126933</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jorgehugo2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-11-29 17:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788127002</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Roy22</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/14.12</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-11-29 18:45:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788127068</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nilsonneptal</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-11-29 19:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788127116</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ayron301208</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/23.04</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-11-29 20:16:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788127119</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>zLewxs</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-11-29 20:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788127140</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>elmerpolinar</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-11-29 20:48:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788127152</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Pope3</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-11-29 20:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788127227</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Patri</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-11-29 22:00:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788127230</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Florest</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-11-29 22:02:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788127257</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Luiggi</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-11-29 22:50:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788127308</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>giampier123</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-11-29 23:52:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788127737</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MAGA18</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/8.54</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-11-30 06:13:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788128085</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>rmfz2025</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-11-30 09:11:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788128163</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>estefani11</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-11-30 09:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788128292</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Jemsynho</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-11-30 10:30:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788128325</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>72501657</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/7.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-11-30 10:51:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788128334</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>raulaquino123</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-11-30 10:52:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788128427</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>chito12</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-11-30 11:34:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788128490</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>yenny</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-11-30 12:02:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788128916</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>fuster3110</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-11-30 15:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788129045</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Amumu0701</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-11-30 16:19:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788129066</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tiznado21</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-11-30 16:29:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788129093</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>raisha9</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-11-30 16:53:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788129228</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>jotacha2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-11-30 18:25:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788129255</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>yO14Ki2006</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-11-30 18:59:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788129318</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>jhijo</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-11-30 19:54:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788129411</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>angelottp</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/95.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-11-30 21:23:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788129435</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Altuna</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-11-30 21:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788129465</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>willmercevall</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:41:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788129483</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>eusmary36</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:54:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>788129507</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Angelo12345</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-11-30 23:23:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>788129525</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Nico_uwu2018</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-11-30 23:50:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>788129534</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>neima</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2025-11-30 23:54:08</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788129921</t>
+          <t>788132114</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seap0706</t>
+          <t>Juana67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-01 06:46:13</t>
+          <t>2025-12-02 00:35:40</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788130062</t>
+          <t>788132666</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>naddia12</t>
+          <t>44906707</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-01 07:45:50</t>
+          <t>2025-12-02 08:15:53</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788130065</t>
+          <t>788132726</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cesar172362</t>
+          <t>Brayangregorio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-01 07:49:01</t>
+          <t>2025-12-02 08:40:35</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788130665</t>
+          <t>788132870</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Andresxdr</t>
+          <t>Marciallima</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-01 11:11:56</t>
+          <t>2025-12-02 09:35:07</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788130803</t>
+          <t>788132966</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>diego22950</t>
+          <t>desalle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/0.37</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-01 11:56:25</t>
+          <t>2025-12-02 10:18:40</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788130983</t>
+          <t>788133017</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JHONHUAYT</t>
+          <t>javiier68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-01 12:56:46</t>
+          <t>2025-12-02 10:41:13</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788131217</t>
+          <t>788133053</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anthonym152023</t>
+          <t>mecasss22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/80.28</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-01 14:12:34</t>
+          <t>2025-12-02 10:56:49</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788131238</t>
+          <t>788133179</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jhonar</t>
+          <t>jumaeldlc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-01 14:18:02</t>
+          <t>2025-12-02 11:47:58</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788131466</t>
+          <t>788133239</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>953468208</t>
+          <t>mento75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-01 16:04:26</t>
+          <t>2025-12-02 12:15:14</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788131478</t>
+          <t>788133245</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>W1lfr3d0</t>
+          <t>Llallirz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-01 16:08:58</t>
+          <t>2025-12-02 12:18:02</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788131505</t>
+          <t>788133362</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LhfvC1963</t>
+          <t>maykeloaiza</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-01 16:16:43</t>
+          <t>2025-12-02 13:01:27</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788131700</t>
+          <t>788133383</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>47677271</t>
+          <t>Silenthill123</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S/40.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-01 18:09:28</t>
+          <t>2025-12-02 13:09:41</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788131769</t>
+          <t>788133431</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Joseluiss</t>
+          <t>Ricardo16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/20.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-01 18:43:43</t>
+          <t>2025-12-02 13:26:08</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788131829</t>
+          <t>788133473</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tukorazom</t>
+          <t>davidtarazona675</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-01 19:24:47</t>
+          <t>2025-12-02 13:40:34</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788131832</t>
+          <t>788133491</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>44314200</t>
+          <t>elixyond2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-01 19:25:19</t>
+          <t>2025-12-02 13:46:54</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788131847</t>
+          <t>788133536</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>elenita288</t>
+          <t>les12302</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-01 19:37:10</t>
+          <t>2025-12-02 13:56:07</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788132006</t>
+          <t>788133617</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>48048204</t>
+          <t>Tanny</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-01 22:37:37</t>
+          <t>2025-12-02 14:24:37</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788132009</t>
+          <t>788133623</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Elda</t>
+          <t>jenner</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-01 22:39:27</t>
+          <t>2025-12-02 14:28:32</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788132045</t>
+          <t>788133638</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bruco99</t>
+          <t>Renar14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,583 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-01 23:22:39</t>
+          <t>2025-12-02 14:37:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>788133668</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mael933</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2025-12-02 14:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>788133695</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gusiev</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2025-12-02 15:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>788133836</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ivfres</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:14:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>788133839</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Eliseoarmas14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S/11.53</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:15:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>788134133</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>callata02</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2025-12-02 18:58:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>788134145</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pinedo02</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2025-12-02 19:06:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>788134166</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>shucawito</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-12-02 19:23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>788134169</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WTDSP2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-12-02 19:31:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788134208</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>greys</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-12-02 20:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788134211</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>marquina123</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-12-02 20:08:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788134241</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>norbilnj</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-12-02 20:31:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788134274</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>herrodri2711</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:22:18</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788132114</t>
+          <t>788138591</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Juana67</t>
+          <t>jose0914</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-02 00:35:40</t>
+          <t>2025-12-05 00:04:13</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788132666</t>
+          <t>788138660</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44906707</t>
+          <t>hernan098</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-02 08:15:53</t>
+          <t>2025-12-05 02:34:05</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788132726</t>
+          <t>788139008</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brayangregorio</t>
+          <t>moralitos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-02 08:40:35</t>
+          <t>2025-12-05 07:46:25</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788132870</t>
+          <t>788139155</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marciallima</t>
+          <t>freddy60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/1.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-02 09:35:07</t>
+          <t>2025-12-05 09:11:25</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788132966</t>
+          <t>788139329</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>desalle</t>
+          <t>Rodcar28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-02 10:18:40</t>
+          <t>2025-12-05 10:45:14</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788133017</t>
+          <t>788139611</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>javiier68</t>
+          <t>Leroy01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-02 10:41:13</t>
+          <t>2025-12-05 12:34:54</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788133053</t>
+          <t>788139662</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mecasss22</t>
+          <t>charlyaquiles</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/105.90</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-02 10:56:49</t>
+          <t>2025-12-05 12:51:58</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788133179</t>
+          <t>788139758</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jumaeldlc</t>
+          <t>vanessa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-02 11:47:58</t>
+          <t>2025-12-05 13:42:36</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788133239</t>
+          <t>788139770</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mento75</t>
+          <t>MARICAL11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-02 12:15:14</t>
+          <t>2025-12-05 13:44:49</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788133245</t>
+          <t>788139962</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Llallirz</t>
+          <t>cristobal61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-02 12:18:02</t>
+          <t>2025-12-05 15:21:24</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788133362</t>
+          <t>788140043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>maykeloaiza</t>
+          <t>Veroka62</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-02 13:01:27</t>
+          <t>2025-12-05 16:20:34</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788133383</t>
+          <t>788140049</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Silenthill123</t>
+          <t>Yasprodendi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-02 13:09:41</t>
+          <t>2025-12-05 16:21:41</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788133431</t>
+          <t>788140058</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ricardo16</t>
+          <t>johancabreram</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S/20.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-02 13:26:08</t>
+          <t>2025-12-05 16:27:33</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788133473</t>
+          <t>788140145</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>davidtarazona675</t>
+          <t>Yersonn</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-02 13:40:34</t>
+          <t>2025-12-05 17:06:28</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788133491</t>
+          <t>788140190</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>elixyond2</t>
+          <t>Eveyo3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S/0.24</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-02 13:46:54</t>
+          <t>2025-12-05 17:38:03</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788133536</t>
+          <t>788140235</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>les12302</t>
+          <t>NEYMARG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S/0.15</t>
+          <t>S/3.67</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-02 13:56:07</t>
+          <t>2025-12-05 18:03:27</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788133617</t>
+          <t>788140280</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tanny</t>
+          <t>maxitho</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-02 14:24:37</t>
+          <t>2025-12-05 18:37:48</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788133623</t>
+          <t>788140301</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jenner</t>
+          <t>YSMALX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-02 14:28:32</t>
+          <t>2025-12-05 18:52:14</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788133638</t>
+          <t>788140334</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Renar14</t>
+          <t>javieralba</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-02 14:37:36</t>
+          <t>2025-12-05 19:49:06</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788133668</t>
+          <t>788140445</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mael933</t>
+          <t>joel2610</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-02 14:56:04</t>
+          <t>2025-12-05 22:01:36</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788133695</t>
+          <t>788140466</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>gusiev</t>
+          <t>VIRNETZX15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-02 15:08:48</t>
+          <t>2025-12-05 22:24:04</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788133836</t>
+          <t>788140487</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ivfres</t>
+          <t>allen1901</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-02 16:14:35</t>
+          <t>2025-12-05 23:12:56</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788133839</t>
+          <t>788140502</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eliseoarmas14</t>
+          <t>Marianita</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/11.53</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-02 16:15:13</t>
+          <t>2025-12-05 23:21:41</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788134133</t>
+          <t>788140508</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>callata02</t>
+          <t>costian2david</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-02 18:58:34</t>
+          <t>2025-12-05 23:23:55</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788134145</t>
+          <t>788140523</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pinedo02</t>
+          <t>richard57</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-02 19:06:57</t>
+          <t>2025-12-05 23:42:26</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788134166</t>
+          <t>788140598</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>shucawito</t>
+          <t>Evelyntavara</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-02 19:23:50</t>
+          <t>2025-12-06 01:23:59</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788134169</t>
+          <t>788140631</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WTDSP2</t>
+          <t>Mechita170554</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-02 19:31:49</t>
+          <t>2025-12-06 02:40:23</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788134208</t>
+          <t>788140751</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>greys</t>
+          <t>fiorellakvllianrumic</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-02 20:08:12</t>
+          <t>2025-12-06 04:26:10</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788134211</t>
+          <t>788140961</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>marquina123</t>
+          <t>Vargas1994</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-12-02 20:08:37</t>
+          <t>2025-12-06 06:22:53</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788134241</t>
+          <t>788141267</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>norbilnj</t>
+          <t>jonasf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-12-02 20:31:58</t>
+          <t>2025-12-06 08:53:30</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788134274</t>
+          <t>788141345</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>herrodri2711</t>
+          <t>David071104</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,3463 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-12-02 21:22:18</t>
+          <t>2025-12-06 09:37:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788141348</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Yurimg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-12-06 09:38:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788141531</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PACHECO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-12-06 10:47:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788141597</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>wil.ng</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-12-06 11:39:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788141606</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Alex35</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-12-06 11:42:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788141612</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>carlos2006</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-12-06 11:46:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788141744</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Blascobh</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-12-06 12:57:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788141834</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>josuecorrea13</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-12-06 13:37:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788141861</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Guillermo1976</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-12-06 13:49:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788141984</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>41244715</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-12-06 14:40:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788141990</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>antonimatias</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-12-06 14:44:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788142041</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>flauber</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-12-06 15:19:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788142140</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>noemy15</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-12-06 16:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788142179</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lavarello1234</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-12-06 16:54:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788142314</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lisbet090</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-12-06 18:55:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788142335</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Naama</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-12-06 19:11:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788142341</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JAKELINECHOCCA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-12-06 19:15:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788142413</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Florlopez</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/113.55</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-12-06 20:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788142422</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>marinrios123</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-12-06 20:29:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788142428</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>miloo123</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-12-06 20:33:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788142446</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>goyo</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-12-06 21:05:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788142458</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>fidelgama123</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-12-06 21:33:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788142461</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jim123456</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-12-06 21:35:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788142488</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>miguel1701</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:24:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788142506</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Lordjen</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-12-06 23:02:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788142536</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SILUGAS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-12-06 23:35:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788142551</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ronaldoelunico96</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-12-06 23:54:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788142674</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chapy05</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/925.70</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-12-07 04:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788142809</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Laste07</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-12-07 05:49:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788142938</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>pameship</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-12-07 06:47:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788143142</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>natius74</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-12-07 08:39:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788143175</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DIAZ27</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-12-07 09:07:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788143280</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>72705313</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-12-07 10:12:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788143328</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sandropaula</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-12-07 10:43:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788143424</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Carmenprieto</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-12-07 11:33:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788143796</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MAR2001.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.02</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-12-07 14:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788143850</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cesar665</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-12-07 14:35:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788143856</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nerinho07</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-12-07 14:39:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788143895</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>romulo40</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-12-07 14:56:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788143931</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>smith7</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-12-07 15:13:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788144042</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>julitomaspi7</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-12-07 16:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788144117</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Shaki</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-12-07 17:23:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788144228</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-12-07 19:09:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788144258</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Xander2024</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-12-07 19:41:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788144264</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>romulito91</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/4.60</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-12-07 19:49:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788144282</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>jersy</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-12-07 20:26:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788144336</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>victor28</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-12-07 21:37:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788144339</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>geidi</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-12-07 21:42:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788144366</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Renzo1502</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.05</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788144420</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Marc09</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-12-07 23:28:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788144474</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>alehen</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-12-08 01:39:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788144525</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Junior08</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-12-08 03:29:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788144555</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Mariat</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-12-08 04:21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788144837</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Germantaza23</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-12-08 07:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788144930</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>eddyr</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-12-08 08:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788144951</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>rociomilagros</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-12-08 09:10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788145167</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>oscar.calderon</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-12-08 11:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788145173</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>naza</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-12-08 11:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788145209</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AngelSaman75</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-12-08 11:24:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788145248</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>vikiq</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-12-08 11:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788145284</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ARESzn</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-12-08 11:53:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788145350</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>jesus77</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-12-08 12:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788145389</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>rudicita</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-12-08 12:54:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788145536</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dayannani06</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/100.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-12-08 14:06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788145569</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>alonso69</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-12-08 14:14:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788145722</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>10616941</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-12-08 15:10:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>788145737</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Jr.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-12-08 15:21:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>788145770</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>toltin</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-12-08 15:32:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>788145812</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>gutierrezW</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2025-12-08 16:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>788146076</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Sullaka10</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2025-12-08 19:01:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>788146100</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>yonathansa</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2025-12-08 19:37:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>788146109</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>pepenorte</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2025-12-08 20:05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>788146139</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>veco123</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2025-12-08 20:30:35</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788146244</t>
+          <t>788150768</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Colones210</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-09 00:35:54</t>
+          <t>2025-12-11 00:15:03</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788146247</t>
+          <t>788150774</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zetianpe1</t>
+          <t>Wildersito</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-09 00:50:20</t>
+          <t>2025-12-11 00:19:05</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788146535</t>
+          <t>788151452</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lisbet</t>
+          <t>kelvyhorna</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-09 06:21:01</t>
+          <t>2025-12-11 08:35:45</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788146859</t>
+          <t>788151461</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43878657</t>
+          <t>Anibalandresbarretop...</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-09 08:40:48</t>
+          <t>2025-12-11 08:39:38</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788147798</t>
+          <t>788151500</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>luislamas</t>
+          <t>Elvispanta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-09 12:36:20</t>
+          <t>2025-12-11 09:06:32</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788147897</t>
+          <t>788151572</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MiloBets</t>
+          <t>Pedrocastilla</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-09 13:07:42</t>
+          <t>2025-12-11 09:41:24</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788147939</t>
+          <t>788151578</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Isabel.80</t>
+          <t>juliocesar96</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-09 13:26:53</t>
+          <t>2025-12-11 09:41:51</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788147972</t>
+          <t>788151581</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Roxy09</t>
+          <t>ej75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-09 13:50:52</t>
+          <t>2025-12-11 09:42:47</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788148059</t>
+          <t>788151587</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dandy95</t>
+          <t>fabiannino2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-09 14:29:04</t>
+          <t>2025-12-11 09:44:11</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788148119</t>
+          <t>788151659</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jacothomas</t>
+          <t>adonis95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-09 15:07:41</t>
+          <t>2025-12-11 10:24:10</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788148218</t>
+          <t>788151677</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yess36</t>
+          <t>adrianito2009000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-09 15:49:33</t>
+          <t>2025-12-11 10:31:24</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788148221</t>
+          <t>788152118</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LeidyQH</t>
+          <t>Veryjos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-09 15:53:20</t>
+          <t>2025-12-11 14:21:18</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788148413</t>
+          <t>788152124</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Darsar30</t>
+          <t>godcar</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-09 17:30:15</t>
+          <t>2025-12-11 14:26:41</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788148428</t>
+          <t>788152148</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ballenixpe</t>
+          <t>pupug</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-09 17:36:35</t>
+          <t>2025-12-11 14:40:58</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788148446</t>
+          <t>788152307</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rodoa2606</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-09 17:50:51</t>
+          <t>2025-12-11 16:07:39</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788148641</t>
+          <t>788152319</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>china06</t>
+          <t>AYRTONMIJAIL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-09 21:55:54</t>
+          <t>2025-12-11 16:13:29</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788148683</t>
+          <t>788152487</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jhoncharles28</t>
+          <t>rafaile27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-09 22:46:38</t>
+          <t>2025-12-11 17:10:31</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788148695</t>
+          <t>788152610</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gustavox123</t>
+          <t>yenuri</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,631 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-09 23:06:21</t>
+          <t>2025-12-11 18:25:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>788152673</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>lea24</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2025-12-11 19:04:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>788152751</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>celviana</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:27:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>788152754</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>karina80</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:31:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>788152769</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lialia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2025-12-11 20:47:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>788152796</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>yampq1414</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2025-12-11 21:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>788152799</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Zoe291720</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2025-12-11 21:24:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>788152826</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lucerolulu</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S/0.41</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2025-12-11 21:53:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>788152829</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mishelfasabi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-12-11 21:55:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>788152835</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>antoni</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-12-11 22:04:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788152856</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sixtozuta</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-12-11 22:40:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788152859</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>abellon</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-12-11 22:41:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788152880</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>elsolitario</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-12-11 23:49:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788152883</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>solis12</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/2.20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-12-11 23:55:02</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788150768</t>
+          <t>788152916</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Katlu.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-11 00:15:03</t>
+          <t>2025-12-12 01:05:14</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788150774</t>
+          <t>788152928</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wildersito</t>
+          <t>nikolas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-11 00:19:05</t>
+          <t>2025-12-12 01:32:00</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788151452</t>
+          <t>788152940</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kelvyhorna</t>
+          <t>Liricosad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-11 08:35:45</t>
+          <t>2025-12-12 02:23:58</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788151461</t>
+          <t>788152955</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anibalandresbarretop...</t>
+          <t>armanqs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-11 08:39:38</t>
+          <t>2025-12-12 02:48:52</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788151500</t>
+          <t>788153066</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Elvispanta</t>
+          <t>ciapris1218</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/0.09</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-11 09:06:32</t>
+          <t>2025-12-12 04:09:26</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788151572</t>
+          <t>788153252</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pedrocastilla</t>
+          <t>jhon2006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-11 09:41:24</t>
+          <t>2025-12-12 06:05:30</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788151578</t>
+          <t>788153309</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>juliocesar96</t>
+          <t>darcam25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-11 09:41:51</t>
+          <t>2025-12-12 06:43:14</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788151581</t>
+          <t>788153354</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ej75</t>
+          <t>Elmer2026ooo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-11 09:42:47</t>
+          <t>2025-12-12 07:15:55</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788151587</t>
+          <t>788153411</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fabiannino2025</t>
+          <t>eybb</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-11 09:44:11</t>
+          <t>2025-12-12 07:46:48</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788151659</t>
+          <t>788153522</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>adonis95</t>
+          <t>Luis1990</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-11 10:24:10</t>
+          <t>2025-12-12 08:46:33</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788151677</t>
+          <t>788153528</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>adrianito2009000</t>
+          <t>Beca90</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-11 10:31:24</t>
+          <t>2025-12-12 08:48:57</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788152118</t>
+          <t>788153564</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Veryjos</t>
+          <t>Luisyucra20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-11 14:21:18</t>
+          <t>2025-12-12 09:08:43</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788152124</t>
+          <t>788153582</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>godcar</t>
+          <t>42714478</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-11 14:26:41</t>
+          <t>2025-12-12 09:13:44</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788152148</t>
+          <t>788153633</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pupug</t>
+          <t>cacherodejhoana</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-11 14:40:58</t>
+          <t>2025-12-12 09:40:17</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788152307</t>
+          <t>788153675</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Zaekni</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-11 16:07:39</t>
+          <t>2025-12-12 09:58:38</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788152319</t>
+          <t>788153696</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AYRTONMIJAIL</t>
+          <t>audante803</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-11 16:13:29</t>
+          <t>2025-12-12 10:06:32</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788152487</t>
+          <t>788153747</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rafaile27</t>
+          <t>William27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-11 17:10:31</t>
+          <t>2025-12-12 10:25:35</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788152610</t>
+          <t>788153810</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yenuri</t>
+          <t>ruiz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-11 18:25:55</t>
+          <t>2025-12-12 10:45:45</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788152673</t>
+          <t>788153879</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lea24</t>
+          <t>kevin45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-11 19:04:55</t>
+          <t>2025-12-12 11:10:59</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788152751</t>
+          <t>788153951</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>celviana</t>
+          <t>ross2003</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-11 20:27:04</t>
+          <t>2025-12-12 11:47:31</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788152754</t>
+          <t>788153987</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>karina80</t>
+          <t>militho</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-11 20:31:35</t>
+          <t>2025-12-12 12:04:12</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788152769</t>
+          <t>788154245</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lialia</t>
+          <t>wiladr05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-11 20:47:19</t>
+          <t>2025-12-12 13:58:48</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788152796</t>
+          <t>788154335</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yampq1414</t>
+          <t>dande</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-11 21:23:10</t>
+          <t>2025-12-12 14:49:38</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788152799</t>
+          <t>788154356</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zoe291720</t>
+          <t>maribelmilagros4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-11 21:24:50</t>
+          <t>2025-12-12 14:58:35</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788152826</t>
+          <t>788154398</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lucerolulu</t>
+          <t>GeroAntoni</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S/0.41</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-11 21:53:50</t>
+          <t>2025-12-12 15:23:11</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788152829</t>
+          <t>788154440</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mishelfasabi</t>
+          <t>12lorenzo12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-11 21:55:46</t>
+          <t>2025-12-12 15:38:54</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788152835</t>
+          <t>788154581</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>antoni</t>
+          <t>liffeles</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-11 22:04:50</t>
+          <t>2025-12-12 17:05:36</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788152856</t>
+          <t>788154629</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sixtozuta</t>
+          <t>Perzival12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-11 22:40:58</t>
+          <t>2025-12-12 17:25:14</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788152859</t>
+          <t>788154677</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abellon</t>
+          <t>desroberro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-12-11 22:41:24</t>
+          <t>2025-12-12 17:55:04</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788152880</t>
+          <t>788154854</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>elsolitario</t>
+          <t>maza1234</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-12-11 23:49:50</t>
+          <t>2025-12-12 19:36:10</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788152883</t>
+          <t>788154875</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>solis12</t>
+          <t>leo222222</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S/2.20</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1960,7 +1960,3127 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-12-11 23:55:02</t>
+          <t>2025-12-12 19:57:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788154908</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Florisa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-12-12 20:32:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788154911</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pamelaju</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-12-12 20:33:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788154977</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Adrianzen</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-12-12 21:34:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788155001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>deymer13</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.16</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-12-12 21:48:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788155022</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>camizaor1225</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:16:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788155028</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Anyell10</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788155037</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>904087880</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788155061</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ronald_Ayaucan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-12-12 23:04:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788155097</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Duberli</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-12-12 23:37:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788155100</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AlexJinez</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-12-12 23:39:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788155553</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>wilson2705</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-12-13 07:23:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788155763</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Alex27</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-12-13 09:02:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788155766</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nolsi1994</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-12-13 09:04:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788155817</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>luis826118</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-12-13 09:17:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788155850</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cangri2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/20.45</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-12-13 09:32:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788156177</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Salazar2007</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-12-13 11:55:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788156312</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gres</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-12-13 12:40:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788156462</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Jack1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-12-13 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788156507</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>brayanquispe25</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-12-13 13:56:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788156528</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NQP2001</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-12-13 14:14:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788156645</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>pinlop86</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.75</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-12-13 14:47:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788156711</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Keyli</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-12-13 15:24:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788156978</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>mybel431</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:33:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788156981</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Yaki</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:35:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788156987</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>waltersitoalt45</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.06</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:38:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788157026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GEORGIAVC124</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-12-13 17:58:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788157065</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Alber10</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:23:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788157074</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>roy03</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:26:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788157104</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>beli83</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:34:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788157134</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jhoyrojas</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-12-13 18:54:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788157242</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>cesar090</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:08:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788157257</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>bebi</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-12-13 20:16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788157320</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>mari1302</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-12-13 21:30:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788157371</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>luiscitopj</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/52.53</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788157440</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>stechiri308</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-12-13 23:43:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788157467</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Aylen16</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-12-14 00:27:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788157497</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>diana1212</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-12-14 00:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788157521</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Almanegra</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-12-14 01:32:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788157569</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>bernal33</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-12-14 03:01:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788157899</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sandoval12</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-12-14 06:54:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788158133</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Daniana</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-12-14 08:59:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788158136</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>EDDYDUDAMEL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-12-14 09:00:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788158184</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>peji</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-12-14 09:25:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788158205</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Armand232427</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-12-14 09:37:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788158238</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>jeanpier96</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-12-14 09:50:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788158307</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Saul0202</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-12-14 10:27:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788158322</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chilcanito</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-12-14 10:33:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788158424</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Kevinz99</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-12-14 11:29:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788158547</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ESA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/27.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-12-14 12:14:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788158559</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Pisco98</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/2.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-12-14 12:19:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788158694</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>belkis123</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-12-14 13:23:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788158772</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>elmago14</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-12-14 13:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788158982</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>KHATHY1799</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-12-14 15:33:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788158997</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Francoyuyarina02</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/3.85</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-12-14 15:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788159075</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>less_lp</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-12-14 16:43:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788159195</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>falcon24</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-12-14 18:09:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788159276</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Stefan2020</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-12-14 19:34:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788159282</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>nestor16</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-12-14 19:41:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788159288</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Elvisvalles</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-12-14 19:43:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788159312</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Robertito</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-12-14 20:05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788159330</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>More26</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-12-14 20:31:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788159363</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>brunella15</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-12-14 21:11:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788159420</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Barzola12</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-12-14 23:02:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788159423</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>mirtha</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-12-14 23:04:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788159429</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>meneses</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.37</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-12-14 23:14:41</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788159444</t>
+          <t>788161403</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>faker12</t>
+          <t>analy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-15 00:09:12</t>
+          <t>2025-12-16 00:23:48</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788159798</t>
+          <t>788161412</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>geraldine</t>
+          <t>luist</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-15 06:45:11</t>
+          <t>2025-12-16 01:01:18</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788159843</t>
+          <t>788161454</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mecanico2015</t>
+          <t>Daneccy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-15 07:09:48</t>
+          <t>2025-12-16 02:30:01</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788159954</t>
+          <t>788161511</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fredysmith10</t>
+          <t>jimixito</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-15 08:03:59</t>
+          <t>2025-12-16 03:20:37</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788160002</t>
+          <t>788161889</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>xupertv26</t>
+          <t>973180584</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-15 08:20:56</t>
+          <t>2025-12-16 07:47:43</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788160143</t>
+          <t>788162045</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jeffersonlt15</t>
+          <t>fraddy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-15 09:39:18</t>
+          <t>2025-12-16 09:17:31</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788160152</t>
+          <t>788162135</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dina</t>
+          <t>isabel1979</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-15 09:44:09</t>
+          <t>2025-12-16 09:57:04</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788160224</t>
+          <t>788162180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fabiola1970</t>
+          <t>kevvvvvv</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S/14.80</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-15 10:15:43</t>
+          <t>2025-12-16 10:20:31</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788160329</t>
+          <t>788162636</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jeraldine</t>
+          <t>otonie282</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-15 11:10:02</t>
+          <t>2025-12-16 13:51:53</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788160338</t>
+          <t>788162696</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Edgardaniel3322</t>
+          <t>Darwink</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-15 11:14:38</t>
+          <t>2025-12-16 14:22:10</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788160344</t>
+          <t>788162783</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>k3k2k1</t>
+          <t>Pablito29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-15 11:14:54</t>
+          <t>2025-12-16 14:58:38</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788160374</t>
+          <t>788162789</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hermiscc</t>
+          <t>Katiuxka</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-15 11:29:25</t>
+          <t>2025-12-16 15:02:38</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788160422</t>
+          <t>788162897</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eswin03</t>
+          <t>araujo123</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-15 11:59:29</t>
+          <t>2025-12-16 15:51:22</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788160497</t>
+          <t>788162957</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JackMz</t>
+          <t>keila</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S/0.02</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-15 12:25:59</t>
+          <t>2025-12-16 16:17:22</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788160560</t>
+          <t>788162996</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>johany21</t>
+          <t>Fredysp</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-15 12:44:35</t>
+          <t>2025-12-16 16:29:32</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788160593</t>
+          <t>788163023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jusmpa</t>
+          <t>danielyamali</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-15 13:00:34</t>
+          <t>2025-12-16 16:38:09</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788160674</t>
+          <t>788163101</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Maikolband</t>
+          <t>Erika123</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-15 14:07:04</t>
+          <t>2025-12-16 17:20:56</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788160773</t>
+          <t>788163104</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loqui</t>
+          <t>artur</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-15 14:54:58</t>
+          <t>2025-12-16 17:21:44</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788160806</t>
+          <t>788163185</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>aleuribe112</t>
+          <t>Jhosmar123</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-15 15:14:24</t>
+          <t>2025-12-16 18:11:37</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788160989</t>
+          <t>788163188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>celestcontr</t>
+          <t>flormariallontopurru...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-15 17:05:49</t>
+          <t>2025-12-16 18:12:40</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788161001</t>
+          <t>788163200</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kafasafa</t>
+          <t>parcero</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-15 17:09:57</t>
+          <t>2025-12-16 18:20:37</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788161103</t>
+          <t>788163215</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mariagarciasupa</t>
+          <t>Esincito</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-15 18:27:17</t>
+          <t>2025-12-16 18:34:02</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788161133</t>
+          <t>788163272</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valeriach</t>
+          <t>Geisy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-15 18:35:38</t>
+          <t>2025-12-16 19:12:28</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788161172</t>
+          <t>788163416</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>antonet</t>
+          <t>Cristianzavala</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S/0.20</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-15 19:08:32</t>
+          <t>2025-12-16 21:06:13</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788161187</t>
+          <t>788163428</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Blanquiazul</t>
+          <t>rayza03</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-15 19:41:10</t>
+          <t>2025-12-16 21:20:09</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788161199</t>
+          <t>788163455</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bicho9</t>
+          <t>Andy2803</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-15 19:46:04</t>
+          <t>2025-12-16 21:42:28</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788161217</t>
+          <t>788163485</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jhusndvy</t>
+          <t>Anderson19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S/0.11</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-15 19:57:14</t>
+          <t>2025-12-16 22:24:33</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788161253</t>
+          <t>788163539</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carlos9907</t>
+          <t>luisdomza19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,391 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-15 20:55:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>788161265</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>mohammed31</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2025-12-15 21:22:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>788161271</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>jampool</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2025-12-15 21:35:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>788161283</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>brian9352</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2025-12-15 21:50:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>788161325</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Andres06</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2025-12-15 22:39:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>788161334</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Josmar123</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2025-12-15 22:46:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>788161349</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ronald313131</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2025-12-15 22:59:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>788161364</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>andro95</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2025-12-15 23:14:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>788161397</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Jhotaguco</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S/0.22</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2025-12-15 23:48:49</t>
+          <t>2025-12-16 23:38:06</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788161403</t>
+          <t>788163554</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>analy</t>
+          <t>bengiecruz1997</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-16 00:23:48</t>
+          <t>2025-12-17 00:14:56</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788161412</t>
+          <t>788163578</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>luist</t>
+          <t>Linton185</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-16 01:01:18</t>
+          <t>2025-12-17 00:25:42</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788161454</t>
+          <t>788163581</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Daneccy</t>
+          <t>tejeda123</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-16 02:30:01</t>
+          <t>2025-12-17 00:25:48</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788161511</t>
+          <t>788163626</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jimixito</t>
+          <t>adolfoorme</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-16 03:20:37</t>
+          <t>2025-12-17 02:30:55</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788161889</t>
+          <t>788163860</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>973180584</t>
+          <t>jaziel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-16 07:47:43</t>
+          <t>2025-12-17 06:00:07</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788162045</t>
+          <t>788163896</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fraddy</t>
+          <t>chiter2012</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-16 09:17:31</t>
+          <t>2025-12-17 06:44:19</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788162135</t>
+          <t>788164046</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>isabel1979</t>
+          <t>Wildor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-16 09:57:04</t>
+          <t>2025-12-17 08:26:07</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788162180</t>
+          <t>788164103</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kevvvvvv</t>
+          <t>Aritum</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-16 10:20:31</t>
+          <t>2025-12-17 08:56:24</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788162636</t>
+          <t>788164133</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>otonie282</t>
+          <t>sonii</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-16 13:51:53</t>
+          <t>2025-12-17 09:28:24</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788162696</t>
+          <t>788164211</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Darwink</t>
+          <t>thaiza</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-16 14:22:10</t>
+          <t>2025-12-17 10:11:35</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788162783</t>
+          <t>788164244</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pablito29</t>
+          <t>yulisaha</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-16 14:58:38</t>
+          <t>2025-12-17 10:26:13</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788162789</t>
+          <t>788164247</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Katiuxka</t>
+          <t>ANGELLLL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-16 15:02:38</t>
+          <t>2025-12-17 10:29:01</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788162897</t>
+          <t>788164397</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>araujo123</t>
+          <t>Marigol</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-16 15:51:22</t>
+          <t>2025-12-17 11:37:51</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788162957</t>
+          <t>788164409</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>keila</t>
+          <t>Aciertalacj</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-16 16:17:22</t>
+          <t>2025-12-17 11:43:07</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788162996</t>
+          <t>788164424</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fredysp</t>
+          <t>PEPITA123</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-16 16:29:32</t>
+          <t>2025-12-17 11:50:40</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788163023</t>
+          <t>788164442</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>danielyamali</t>
+          <t>teffy25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-16 16:38:09</t>
+          <t>2025-12-17 12:00:38</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788163101</t>
+          <t>788164526</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Erika123</t>
+          <t>oliza</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-16 17:20:56</t>
+          <t>2025-12-17 12:58:48</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788163104</t>
+          <t>788164712</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>artur</t>
+          <t>osita</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-16 17:21:44</t>
+          <t>2025-12-17 14:19:17</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788163185</t>
+          <t>788164805</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jhosmar123</t>
+          <t>Angelitoisla</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-16 18:11:37</t>
+          <t>2025-12-17 15:25:57</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788163188</t>
+          <t>788164811</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flormariallontopurru...</t>
+          <t>48660850</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.72</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-16 18:12:40</t>
+          <t>2025-12-17 15:26:17</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788163200</t>
+          <t>788164886</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>parcero</t>
+          <t>orlando2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-16 18:20:37</t>
+          <t>2025-12-17 16:11:28</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788163215</t>
+          <t>788164895</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Esincito</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-16 18:34:02</t>
+          <t>2025-12-17 16:20:56</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788163272</t>
+          <t>788164919</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Geisy</t>
+          <t>marielidia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-16 19:12:28</t>
+          <t>2025-12-17 16:37:16</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788163416</t>
+          <t>788164997</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cristianzavala</t>
+          <t>Gianzilla</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-16 21:06:13</t>
+          <t>2025-12-17 17:48:12</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788163428</t>
+          <t>788165069</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rayza03</t>
+          <t>soledad2001..</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-16 21:20:09</t>
+          <t>2025-12-17 18:53:02</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788163455</t>
+          <t>788165123</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Andy2803</t>
+          <t>Ever12345</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-16 21:42:28</t>
+          <t>2025-12-17 19:58:20</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788163485</t>
+          <t>788165222</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Anderson19</t>
+          <t>ruthdelmith</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-16 22:24:33</t>
+          <t>2025-12-17 22:25:56</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788163539</t>
+          <t>788165231</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>luisdomza19</t>
+          <t>Jarissa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,151 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-16 23:38:06</t>
+          <t>2025-12-17 22:33:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788165246</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Erick-grone</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:58:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788165249</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Azcino</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/50.10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-12-17 23:16:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788165258</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rubencq</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-12-17 23:27:05</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788163554</t>
+          <t>788165327</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bengiecruz1997</t>
+          <t>mau21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-17 00:14:56</t>
+          <t>2025-12-18 02:12:47</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788163578</t>
+          <t>788165354</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Linton185</t>
+          <t>dian123</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-17 00:25:42</t>
+          <t>2025-12-18 03:33:23</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788163581</t>
+          <t>788165594</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tejeda123</t>
+          <t>juarezdm02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-17 00:25:48</t>
+          <t>2025-12-18 05:44:21</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788163626</t>
+          <t>788165732</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>adolfoorme</t>
+          <t>Leandro24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-17 02:30:55</t>
+          <t>2025-12-18 07:16:50</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788163860</t>
+          <t>788165822</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jaziel</t>
+          <t>SkylinexD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-17 06:00:07</t>
+          <t>2025-12-18 08:22:02</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788163896</t>
+          <t>788165837</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>chiter2012</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-17 06:44:19</t>
+          <t>2025-12-18 08:30:06</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788164046</t>
+          <t>788165942</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wildor</t>
+          <t>bartosrn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-17 08:26:07</t>
+          <t>2025-12-18 09:14:46</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788164103</t>
+          <t>788166164</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aritum</t>
+          <t>44417624</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S/0.19</t>
+          <t>S/0.90</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-17 08:56:24</t>
+          <t>2025-12-18 11:11:25</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788164133</t>
+          <t>788166311</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sonii</t>
+          <t>jiorllinia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-17 09:28:24</t>
+          <t>2025-12-18 12:11:40</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788164211</t>
+          <t>788166368</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>thaiza</t>
+          <t>gayanunez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-17 10:11:35</t>
+          <t>2025-12-18 12:37:31</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788164244</t>
+          <t>788166395</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yulisaha</t>
+          <t>1646133</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.48</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-17 10:26:13</t>
+          <t>2025-12-18 12:51:10</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788164247</t>
+          <t>788166575</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANGELLLL</t>
+          <t>Robalon1178</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-17 10:29:01</t>
+          <t>2025-12-18 14:02:11</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788164397</t>
+          <t>788166614</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Marigol</t>
+          <t>Maura.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-17 11:37:51</t>
+          <t>2025-12-18 14:36:01</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788164409</t>
+          <t>788166692</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aciertalacj</t>
+          <t>jorge1jhfa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-17 11:43:07</t>
+          <t>2025-12-18 15:45:16</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788164424</t>
+          <t>788166788</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PEPITA123</t>
+          <t>rosanazavaletasilva1...</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-17 11:50:40</t>
+          <t>2025-12-18 16:39:17</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788164442</t>
+          <t>788166866</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>teffy25</t>
+          <t>joel0520</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/50.08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-17 12:00:38</t>
+          <t>2025-12-18 17:27:57</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788164526</t>
+          <t>788166884</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>oliza</t>
+          <t>super</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-17 12:58:48</t>
+          <t>2025-12-18 17:43:16</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788164712</t>
+          <t>788166968</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>osita</t>
+          <t>hicler</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-17 14:19:17</t>
+          <t>2025-12-18 18:48:19</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788164805</t>
+          <t>788166986</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Angelitoisla</t>
+          <t>Ivanc66</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-17 15:25:57</t>
+          <t>2025-12-18 18:55:48</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788164811</t>
+          <t>788167139</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>48660850</t>
+          <t>Alexcahuana</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S/0.72</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-17 15:26:17</t>
+          <t>2025-12-18 21:07:56</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788164886</t>
+          <t>788167169</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>orlando2</t>
+          <t>cachaco</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-17 16:11:28</t>
+          <t>2025-12-18 21:49:19</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788164895</t>
+          <t>788167178</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>abram</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-17 16:20:56</t>
+          <t>2025-12-18 21:58:24</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788164919</t>
+          <t>788167208</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>marielidia</t>
+          <t>nilserayo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-17 16:37:16</t>
+          <t>2025-12-18 22:46:04</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788164997</t>
+          <t>788167220</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gianzilla</t>
+          <t>Gaby2609</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,343 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-17 17:48:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>788165069</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>soledad2001..</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2025-12-17 18:53:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>788165123</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ever12345</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2025-12-17 19:58:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>788165222</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ruthdelmith</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S/0.20</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2025-12-17 22:25:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>788165231</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Jarissa</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2025-12-17 22:33:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>788165246</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Erick-grone</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2025-12-17 22:58:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>788165249</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Azcino</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S/50.10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2025-12-17 23:16:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>788165258</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Rubencq</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2025-12-17 23:27:05</t>
+          <t>2025-12-18 23:30:22</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788165327</t>
+          <t>788167253</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mau21</t>
+          <t>Payolo2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S/0.05</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-18 02:12:47</t>
+          <t>2025-12-19 00:17:44</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788165354</t>
+          <t>788167265</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dian123</t>
+          <t>minerba1212</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.25</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-18 03:33:23</t>
+          <t>2025-12-19 00:37:58</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788165594</t>
+          <t>788167625</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>juarezdm02</t>
+          <t>eddyalexanderseminar...</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-18 05:44:21</t>
+          <t>2025-12-19 06:26:00</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788165732</t>
+          <t>788167772</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leandro24</t>
+          <t>kiara203</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-18 07:16:50</t>
+          <t>2025-12-19 07:36:51</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788165822</t>
+          <t>788167979</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SkylinexD</t>
+          <t>Harold1995</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-18 08:22:02</t>
+          <t>2025-12-19 09:07:22</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788165837</t>
+          <t>788168204</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Jakeline</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-18 08:30:06</t>
+          <t>2025-12-19 10:36:15</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788165942</t>
+          <t>788168360</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bartosrn</t>
+          <t>Javier1415</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-18 09:14:46</t>
+          <t>2025-12-19 11:54:08</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788166164</t>
+          <t>788168450</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>44417624</t>
+          <t>Henderson786</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S/0.90</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-18 11:11:25</t>
+          <t>2025-12-19 12:28:29</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788166311</t>
+          <t>788168468</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jiorllinia</t>
+          <t>jrsnlc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-18 12:11:40</t>
+          <t>2025-12-19 12:37:46</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788166368</t>
+          <t>788168636</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gayanunez</t>
+          <t>Impulsor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-18 12:37:31</t>
+          <t>2025-12-19 14:00:23</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788166395</t>
+          <t>788168681</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1646133</t>
+          <t>alesa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S/0.48</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-18 12:51:10</t>
+          <t>2025-12-19 14:25:51</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788166575</t>
+          <t>788168717</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Robalon1178</t>
+          <t>44633941</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-18 14:02:11</t>
+          <t>2025-12-19 15:00:04</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788166614</t>
+          <t>788168849</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maura.</t>
+          <t>piurano27</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.33</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-18 14:36:01</t>
+          <t>2025-12-19 15:30:10</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788166692</t>
+          <t>788168912</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jorge1jhfa</t>
+          <t>anacludia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-18 15:45:16</t>
+          <t>2025-12-19 16:04:53</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788166788</t>
+          <t>788169197</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rosanazavaletasilva1...</t>
+          <t>chocylo123</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-18 16:39:17</t>
+          <t>2025-12-19 19:10:27</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788166866</t>
+          <t>788169203</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>joel0520</t>
+          <t>Abrahn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S/50.08</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-18 17:27:57</t>
+          <t>2025-12-19 19:13:58</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788166884</t>
+          <t>788169230</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>super</t>
+          <t>guardiola</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-18 17:43:16</t>
+          <t>2025-12-19 20:00:40</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788166968</t>
+          <t>788169242</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hicler</t>
+          <t>Leo-Orion</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-18 18:48:19</t>
+          <t>2025-12-19 20:08:07</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788166986</t>
+          <t>788169293</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ivanc66</t>
+          <t>EITHAN13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-18 18:55:48</t>
+          <t>2025-12-19 20:50:32</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788167139</t>
+          <t>788169314</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alexcahuana</t>
+          <t>guille55</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-18 21:07:56</t>
+          <t>2025-12-19 21:01:01</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788167169</t>
+          <t>788169332</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cachaco</t>
+          <t>nonis_ca</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-18 21:49:19</t>
+          <t>2025-12-19 21:27:01</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788167178</t>
+          <t>788169359</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abram</t>
+          <t>carlitos12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-18 21:58:24</t>
+          <t>2025-12-19 21:55:51</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788167208</t>
+          <t>788169389</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nilserayo</t>
+          <t>edu7w</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-18 22:46:04</t>
+          <t>2025-12-19 22:35:05</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788167220</t>
+          <t>788169446</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gaby2609</t>
+          <t>Angienaye3011</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,3559 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-18 23:30:22</t>
+          <t>2025-12-20 00:01:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>788169503</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Angelles</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2025-12-20 01:07:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>788169536</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MarcosTE28</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-12-20 02:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>788169575</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ianjosue</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-12-20 03:01:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788169608</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Miki2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-12-20 03:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788169746</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Frank01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-12-20 05:32:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788169872</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>juanelsabroso12345</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-12-20 06:41:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788169875</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>marylliamunasca26</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-12-20 06:41:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788170085</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>clarissadelvaz</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-12-20 08:02:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788170256</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VictorHuaman</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-12-20 09:17:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788170271</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Depor777</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-12-20 09:26:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788170307</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>roelpelileocoquinche</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-12-20 09:41:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788170313</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>darioh19</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-12-20 09:43:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788170385</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jeanMFA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-12-20 10:27:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788170388</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>280417</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-12-20 10:29:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788170412</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jeison0629</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-12-20 10:47:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788170415</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nibram2002</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-12-20 10:47:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788170490</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dianacordova27</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-12-20 11:13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788170727</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Deyber</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-12-20 13:02:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788170853</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fredi0110</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-12-20 13:47:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788170907</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>niria1234</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-12-20 13:58:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788170982</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>IAMMAX</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:39:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788170997</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>zoilia2529</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-12-20 14:51:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788171042</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>leito73</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-12-20 15:19:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788171090</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lili21</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-12-20 15:58:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>788171204</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vnes12</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-12-20 17:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>788171228</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>babitas83</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S/0.15</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-12-20 17:30:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>788171255</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>erika09</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025-12-20 17:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>788171288</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>esther</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-12-20 18:19:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>788171333</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>chota123</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2025-12-20 18:34:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>788171336</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>machimito29</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2025-12-20 18:34:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>788171465</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Clifton</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-12-20 20:44:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>788171480</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gayma</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-12-20 20:55:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>788171498</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>anitaacosta123</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-12-20 21:30:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>788171519</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>josely</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2025-12-20 22:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>788171534</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ritos</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S/0.05</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-12-20 22:27:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>788171588</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>falcomxd</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-12-20 23:57:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>788171606</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>tokiita7</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2025-12-21 00:37:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>788171612</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Boxer1718</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2025-12-21 00:40:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>788171660</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Jazyiyi13</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2025-12-21 03:00:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>788171906</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>pao27h</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2025-12-21 06:43:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>788172089</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>apachas</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2025-12-21 08:24:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>788172107</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Neiwiss</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2025-12-21 08:30:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>788172134</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Alias_Mori</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-12-21 08:43:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>788172248</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nohe2007</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-12-21 09:24:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>788172314</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Yura02</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-12-21 10:06:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>788172521</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Niltonzz067</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-12-21 12:06:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>788172623</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>eegrosas</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-12-21 13:14:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>788172656</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>davidmiguel</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-12-21 13:41:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>788172674</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Joewilcm945</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-12-21 13:54:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>788172692</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PAOLI</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-12-21 14:02:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>788172740</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>leona21</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2025-12-21 14:34:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>788172746</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Reo2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2025-12-21 14:36:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>788172806</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>lola</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2025-12-21 15:19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>788172857</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>splinter2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2025-12-21 15:56:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>788172905</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>antuanezitha11</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2025-12-21 16:51:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>788172977</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MERLO03</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2025-12-21 17:42:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>788173007</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>newton</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2025-12-21 18:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>788173025</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Francisco0378</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2025-12-21 18:42:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>788173028</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Antoniczj</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-12-21 18:43:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>788173040</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>gustavolee</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2025-12-21 19:05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>788173046</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ElidaCQ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2025-12-21 19:10:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>788173061</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ANGELOQV</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2025-12-21 19:29:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>788173073</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>elzarate</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2025-12-21 19:32:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>788173085</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>piter12</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2025-12-21 19:36:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>788173106</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tefa3020</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2025-12-21 19:58:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>788173127</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Socorro2212</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2025-12-21 20:20:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>788173145</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>keiko</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2025-12-21 20:49:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>788173172</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Roberto505</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2025-12-21 21:07:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>788173196</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Maria05</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2025-12-21 21:30:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>788173199</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sanz</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2025-12-21 21:42:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>788173205</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>lumy</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2025-12-21 21:47:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>788173208</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>maria10</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2025-12-21 21:48:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>788173244</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>dolibeth2601</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2025-12-21 22:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>788173265</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>rossa_castro</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2025-12-21 22:55:35</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788173379</t>
+          <t>788175119</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Juniormarina</t>
+          <t>Maryangel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-22 02:39:50</t>
+          <t>2025-12-23 00:38:29</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788173529</t>
+          <t>788175137</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cesareduardo</t>
+          <t>Riverluis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-22 05:13:50</t>
+          <t>2025-12-23 01:43:49</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788173682</t>
+          <t>788175419</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cualiro</t>
+          <t>jorgevv27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-22 07:01:00</t>
+          <t>2025-12-23 06:23:47</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788173793</t>
+          <t>788175605</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GoonideuS</t>
+          <t>lovecita</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-22 08:18:06</t>
+          <t>2025-12-23 07:43:28</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788173856</t>
+          <t>788175683</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kendan</t>
+          <t>hitlertuanama</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/528.10</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-22 09:07:03</t>
+          <t>2025-12-23 08:28:37</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788173862</t>
+          <t>788175695</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HerlindaBeria</t>
+          <t>Aristides</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-22 09:08:23</t>
+          <t>2025-12-23 08:34:17</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788173940</t>
+          <t>788175713</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>joseleonida11</t>
+          <t>sofia1234</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-22 09:56:17</t>
+          <t>2025-12-23 08:45:18</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788173985</t>
+          <t>788175806</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18eli</t>
+          <t>Trigy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-22 10:24:33</t>
+          <t>2025-12-23 09:38:16</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788174000</t>
+          <t>788175824</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PruebaFM</t>
+          <t>antonyy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.40</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-22 10:31:30</t>
+          <t>2025-12-23 09:44:56</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788174078</t>
+          <t>788175857</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mayra2930</t>
+          <t>GERALGR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-22 11:29:40</t>
+          <t>2025-12-23 09:59:42</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788174324</t>
+          <t>788175959</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>82889</t>
+          <t>Goleen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-22 13:38:22</t>
+          <t>2025-12-23 10:53:56</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788174357</t>
+          <t>788176001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Royberia21</t>
+          <t>camargo1992</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-22 13:50:26</t>
+          <t>2025-12-23 11:20:14</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788174432</t>
+          <t>788176211</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>patico</t>
+          <t>T05Loreto</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-22 14:22:24</t>
+          <t>2025-12-23 12:50:22</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788174468</t>
+          <t>788176259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vjb22</t>
+          <t>edson20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-22 14:52:26</t>
+          <t>2025-12-23 13:06:19</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788174543</t>
+          <t>788176280</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>randy07</t>
+          <t>744779</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-22 15:27:10</t>
+          <t>2025-12-23 13:20:55</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788174567</t>
+          <t>788176304</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1ori</t>
+          <t>joue</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-22 15:32:54</t>
+          <t>2025-12-23 13:35:46</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788174570</t>
+          <t>788176427</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>weu3i</t>
+          <t>Luli</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-22 15:37:09</t>
+          <t>2025-12-23 14:54:29</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788174642</t>
+          <t>788176511</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yangarcia</t>
+          <t>Juancarlos1986</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-22 16:21:36</t>
+          <t>2025-12-23 15:19:52</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788174777</t>
+          <t>788176535</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Smith24</t>
+          <t>Pachjnflup</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-22 17:31:04</t>
+          <t>2025-12-23 15:28:06</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788174786</t>
+          <t>788176571</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felixdiaz</t>
+          <t>imanol28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-22 17:37:20</t>
+          <t>2025-12-23 15:39:55</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788174822</t>
+          <t>788176613</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zaid2525</t>
+          <t>ClaraRos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S/102.60</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-22 18:06:56</t>
+          <t>2025-12-23 15:53:14</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788174879</t>
+          <t>788176640</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jazTM22</t>
+          <t>Jose2800</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-22 19:02:51</t>
+          <t>2025-12-23 16:02:47</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788174900</t>
+          <t>788176646</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>evansbayron</t>
+          <t>MiguelPerez2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/63.50</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-22 19:25:05</t>
+          <t>2025-12-23 16:06:18</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788174966</t>
+          <t>788176652</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Maycol123</t>
+          <t>lizbeth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-22 20:34:45</t>
+          <t>2025-12-23 16:11:50</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788175005</t>
+          <t>788176757</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jonercito14</t>
+          <t>milagroschina</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-22 21:18:34</t>
+          <t>2025-12-23 17:00:05</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788175008</t>
+          <t>788176880</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Acuario</t>
+          <t>dennisx96</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-22 21:19:24</t>
+          <t>2025-12-23 18:12:28</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788175083</t>
+          <t>788176955</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>julio1000</t>
+          <t>anthony0987</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-22 23:17:01</t>
+          <t>2025-12-23 18:57:12</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788175089</t>
+          <t>788177006</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Juliana000</t>
+          <t>me</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1816,7 +1816,391 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-22 23:45:01</t>
+          <t>2025-12-23 19:50:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788177018</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mayerlilluen</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-12-23 20:02:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>788177063</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>T1Loreto</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-12-23 20:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>788177078</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>T1-Loreto</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-12-23 20:55:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>788177084</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>anthny123</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-12-23 20:59:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>788177114</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jai1275</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-12-23 21:28:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>788177123</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jeinercito.37</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-12-23 21:47:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>788177129</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bryantc22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-12-23 21:53:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>788177183</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>leito05</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-12-23 23:46:11</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788175119</t>
+          <t>788177213</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Maryangel</t>
+          <t>Priscila</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-23 00:38:29</t>
+          <t>2025-12-24 00:58:03</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788175137</t>
+          <t>788177219</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Riverluis</t>
+          <t>elvis33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/3.61</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-23 01:43:49</t>
+          <t>2025-12-24 01:05:02</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788175419</t>
+          <t>788177342</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jorgevv27</t>
+          <t>JCHD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-23 06:23:47</t>
+          <t>2025-12-24 05:13:26</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788175605</t>
+          <t>788177441</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lovecita</t>
+          <t>juanR1994</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-23 07:43:28</t>
+          <t>2025-12-24 06:07:15</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788175683</t>
+          <t>788177507</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hitlertuanama</t>
+          <t>Garate</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-23 08:28:37</t>
+          <t>2025-12-24 06:57:04</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788175695</t>
+          <t>788177540</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aristides</t>
+          <t>layza1993</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-23 08:34:17</t>
+          <t>2025-12-24 07:14:45</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788175713</t>
+          <t>788177642</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sofia1234</t>
+          <t>cord</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/0.14</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-23 08:45:18</t>
+          <t>2025-12-24 08:31:56</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788175806</t>
+          <t>788177738</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trigy</t>
+          <t>Juanca41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-23 09:38:16</t>
+          <t>2025-12-24 09:37:18</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788175824</t>
+          <t>788177741</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>antonyy</t>
+          <t>kevin123x</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S/0.40</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-23 09:44:56</t>
+          <t>2025-12-24 09:37:24</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788175857</t>
+          <t>788177777</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GERALGR</t>
+          <t>racso20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S/0.13</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-23 09:59:42</t>
+          <t>2025-12-24 09:54:41</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788175959</t>
+          <t>788177792</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Goleen</t>
+          <t>twJeremi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-23 10:53:56</t>
+          <t>2025-12-24 10:10:56</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788176001</t>
+          <t>788177876</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>camargo1992</t>
+          <t>Anirous</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-23 11:20:14</t>
+          <t>2025-12-24 11:01:02</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788176211</t>
+          <t>788177972</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T05Loreto</t>
+          <t>lime22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-23 12:50:22</t>
+          <t>2025-12-24 11:54:18</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788176259</t>
+          <t>788178092</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>edson20</t>
+          <t>Marshita</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-23 13:06:19</t>
+          <t>2025-12-24 12:52:50</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788176280</t>
+          <t>788178143</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>744779</t>
+          <t>Mpulache84.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-23 13:20:55</t>
+          <t>2025-12-24 13:28:57</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788176304</t>
+          <t>788178233</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>joue</t>
+          <t>Jefferson28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-23 13:35:46</t>
+          <t>2025-12-24 14:11:07</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788176427</t>
+          <t>788178299</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Luli</t>
+          <t>charito1981</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-23 14:54:29</t>
+          <t>2025-12-24 14:49:32</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788176511</t>
+          <t>788178380</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Juancarlos1986</t>
+          <t>Templado08</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-23 15:19:52</t>
+          <t>2025-12-24 15:26:19</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788176535</t>
+          <t>788178416</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pachjnflup</t>
+          <t>3036alex</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-23 15:28:06</t>
+          <t>2025-12-24 15:31:29</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788176571</t>
+          <t>788178452</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>imanol28</t>
+          <t>jeferson.dsvila</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-23 15:39:55</t>
+          <t>2025-12-24 15:42:03</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788176613</t>
+          <t>788178461</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ClaraRos</t>
+          <t>Chatoo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-23 15:53:14</t>
+          <t>2025-12-24 15:43:08</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788176640</t>
+          <t>788178491</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jose2800</t>
+          <t>Keima2022</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-23 16:02:47</t>
+          <t>2025-12-24 16:13:36</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788176646</t>
+          <t>788178536</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MiguelPerez2</t>
+          <t>chula26</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/63.50</t>
+          <t>S/0.91</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-23 16:06:18</t>
+          <t>2025-12-24 16:36:01</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788176652</t>
+          <t>788178548</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>lizbeth</t>
+          <t>Benett</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-23 16:11:50</t>
+          <t>2025-12-24 16:43:57</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788176757</t>
+          <t>788178728</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>milagroschina</t>
+          <t>angelm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-23 17:00:05</t>
+          <t>2025-12-24 17:38:42</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788176880</t>
+          <t>788178905</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dennisx96</t>
+          <t>maricielo0oo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-23 18:12:28</t>
+          <t>2025-12-24 18:31:58</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788176955</t>
+          <t>788178965</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>anthony0987</t>
+          <t>Daniel1976</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-23 18:57:12</t>
+          <t>2025-12-24 18:43:22</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788177006</t>
+          <t>788178992</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>Grecoromano1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-23 19:50:37</t>
+          <t>2025-12-24 18:50:07</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788177018</t>
+          <t>788179013</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mayerlilluen</t>
+          <t>09360861</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-12-23 20:02:56</t>
+          <t>2025-12-24 19:03:42</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788177063</t>
+          <t>788179130</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T1Loreto</t>
+          <t>Janeth48</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-12-23 20:51:17</t>
+          <t>2025-12-24 20:04:16</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788177078</t>
+          <t>788179193</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T1-Loreto</t>
+          <t>joseleh</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-12-23 20:55:43</t>
+          <t>2025-12-24 21:54:11</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>788177084</t>
+          <t>788179307</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>anthny123</t>
+          <t>avi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-12-23 20:59:58</t>
+          <t>2025-12-25 01:31:32</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>788177114</t>
+          <t>788179580</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jai1275</t>
+          <t>Jessenia04</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-12-23 21:28:00</t>
+          <t>2025-12-25 04:33:05</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>788177123</t>
+          <t>788180150</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jeinercito.37</t>
+          <t>Joseherreraquispe</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-12-23 21:47:15</t>
+          <t>2025-12-25 10:15:13</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>788177129</t>
+          <t>788180291</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bryantc22</t>
+          <t>lourdessita</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-12-23 21:53:42</t>
+          <t>2025-12-25 11:52:32</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>788177183</t>
+          <t>788180348</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>leito05</t>
+          <t>taya15</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2200,7 +2200,583 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-12-23 23:46:11</t>
+          <t>2025-12-25 12:28:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>788180354</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lulu321</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-12-25 12:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>788180450</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jimura</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-12-25 13:23:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>788180462</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>lalicha25</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S/66.09</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-12-25 13:40:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>788180531</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>alison</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-12-25 14:28:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>788180534</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Kely</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2025-12-25 14:31:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>788180927</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>derwin</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-12-25 19:03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>788180996</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>William2507</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-12-25 20:12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>788181047</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>JosueBsndido</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-12-25 21:05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>788181065</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DarioC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2025-12-25 21:26:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>788181077</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ALEBRICIO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-12-25 21:54:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>788181161</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>alexito1234</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-12-25 23:41:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>788181167</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Scristal2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025-12-25 23:57:33</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788177213</t>
+          <t>788181200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Priscila</t>
+          <t>leugimrb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-24 00:58:03</t>
+          <t>2025-12-26 01:33:36</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788177219</t>
+          <t>788181443</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>elvis33</t>
+          <t>polis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/3.61</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-24 01:05:02</t>
+          <t>2025-12-26 05:47:43</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788177342</t>
+          <t>788181620</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JCHD</t>
+          <t>kikin23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-24 05:13:26</t>
+          <t>2025-12-26 06:38:26</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788177441</t>
+          <t>788181746</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>juanR1994</t>
+          <t>Rodri1508</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-24 06:07:15</t>
+          <t>2025-12-26 07:38:54</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788177507</t>
+          <t>788181755</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Garate</t>
+          <t>gianfrankosn</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-24 06:57:04</t>
+          <t>2025-12-26 07:42:12</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788177540</t>
+          <t>788181794</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>layza1993</t>
+          <t>cleydiestrada</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-24 07:14:45</t>
+          <t>2025-12-26 08:14:30</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788177642</t>
+          <t>788181992</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cord</t>
+          <t>JUAN2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-24 08:31:56</t>
+          <t>2025-12-26 09:53:52</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788177738</t>
+          <t>788182085</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Juanca41</t>
+          <t>Zizu2084</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-24 09:37:18</t>
+          <t>2025-12-26 10:30:01</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788177741</t>
+          <t>788182106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kevin123x</t>
+          <t>sagitario031280</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-24 09:37:24</t>
+          <t>2025-12-26 10:35:56</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788177777</t>
+          <t>788182421</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>racso20</t>
+          <t>cielo3255</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-24 09:54:41</t>
+          <t>2025-12-26 12:55:11</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788177792</t>
+          <t>788182511</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>twJeremi</t>
+          <t>Pieroale12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-24 10:10:56</t>
+          <t>2025-12-26 13:41:42</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788177876</t>
+          <t>788182580</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Anirous</t>
+          <t>aldacr</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-24 11:01:02</t>
+          <t>2025-12-26 14:04:36</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788177972</t>
+          <t>788182592</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lime22</t>
+          <t>deisyalina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-24 11:54:18</t>
+          <t>2025-12-26 14:11:43</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788178092</t>
+          <t>788182619</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marshita</t>
+          <t>DjAbelSanchez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-24 12:52:50</t>
+          <t>2025-12-26 14:18:30</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788178143</t>
+          <t>788182649</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mpulache84.</t>
+          <t>Jeanss</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-24 13:28:57</t>
+          <t>2025-12-26 14:27:33</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788178233</t>
+          <t>788182667</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jefferson28</t>
+          <t>liviapoma123</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-12-24 14:11:07</t>
+          <t>2025-12-26 14:32:56</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788178299</t>
+          <t>788182802</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>charito1981</t>
+          <t>danko</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-24 14:49:32</t>
+          <t>2025-12-26 15:28:51</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788178380</t>
+          <t>788182859</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Templado08</t>
+          <t>Chemo7319</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S/0.35</t>
+          <t>S/0.75</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-12-24 15:26:19</t>
+          <t>2025-12-26 15:47:53</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788178416</t>
+          <t>788182883</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3036alex</t>
+          <t>45853760</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.37</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-12-24 15:31:29</t>
+          <t>2025-12-26 16:01:27</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788178452</t>
+          <t>788182904</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jeferson.dsvila</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-12-24 15:42:03</t>
+          <t>2025-12-26 16:18:11</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>788178461</t>
+          <t>788183165</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chatoo</t>
+          <t>cynthiach</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-12-24 15:43:08</t>
+          <t>2025-12-26 19:30:44</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>788178491</t>
+          <t>788183201</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Keima2022</t>
+          <t>Lesly15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S/0.25</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-12-24 16:13:36</t>
+          <t>2025-12-26 19:52:23</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>788178536</t>
+          <t>788183963</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>chula26</t>
+          <t>Gerisa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S/0.91</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-12-24 16:36:01</t>
+          <t>2025-12-27 08:27:03</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>788178548</t>
+          <t>788183990</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Benett</t>
+          <t>PDRN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/150.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-12-24 16:43:57</t>
+          <t>2025-12-27 08:42:03</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>788178728</t>
+          <t>788184080</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>angelm</t>
+          <t>leydyls</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-12-24 17:38:42</t>
+          <t>2025-12-27 09:43:34</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>788178905</t>
+          <t>788184149</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>maricielo0oo</t>
+          <t>ramiro95</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-12-24 18:31:58</t>
+          <t>2025-12-27 10:20:25</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>788178965</t>
+          <t>788184446</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Daniel1976</t>
+          <t>joseiza37</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-12-24 18:43:22</t>
+          <t>2025-12-27 12:55:03</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>788178992</t>
+          <t>788184734</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Grecoromano1</t>
+          <t>grupocyeingenieros</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>S/0.22</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-12-24 18:50:07</t>
+          <t>2025-12-27 16:24:43</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>788179013</t>
+          <t>788184809</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>09360861</t>
+          <t>Nata</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-12-24 19:03:42</t>
+          <t>2025-12-27 17:14:36</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>788179130</t>
+          <t>788186000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Janeth48</t>
+          <t>Condezo888</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-12-24 20:04:16</t>
+          <t>2025-12-28 10:33:37</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>788179193</t>
+          <t>788186486</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>joseleh</t>
+          <t>GARCIA13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-12-24 21:54:11</t>
+          <t>2025-12-28 14:50:26</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>788179307</t>
+          <t>788186621</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>avi</t>
+          <t>Josu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-12-25 01:31:32</t>
+          <t>2025-12-28 16:13:37</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>788179580</t>
+          <t>788186705</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jessenia04</t>
+          <t>jk</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2056,727 +2056,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-12-25 04:33:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>788180150</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Joseherreraquispe</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2025-12-25 10:15:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>788180291</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>lourdessita</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2025-12-25 11:52:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>788180348</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>taya15</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2025-12-25 12:28:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>788180354</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Lulu321</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2025-12-25 12:29:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>788180450</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Jimura</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2025-12-25 13:23:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>788180462</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>lalicha25</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S/66.09</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2025-12-25 13:40:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>788180531</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>alison</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2025-12-25 14:28:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>788180534</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Kely</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2025-12-25 14:31:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>788180927</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>derwin</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2025-12-25 19:03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>788180996</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>William2507</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2025-12-25 20:12:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>788181047</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>JosueBsndido</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2025-12-25 21:05:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>788181065</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>DarioC</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2025-12-25 21:26:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>788181077</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ALEBRICIO</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2025-12-25 21:54:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>788181161</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>alexito1234</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2025-12-25 23:41:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>788181167</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Scristal2025</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2025-12-25 23:57:33</t>
+          <t>2025-12-28 17:21:58</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788187677</t>
+          <t>788189876</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>aderly9</t>
+          <t>Bettito1972</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S/0.37</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-29 09:15:28</t>
+          <t>2025-12-30 09:14:35</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788187800</t>
+          <t>788190101</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>temorivera</t>
+          <t>gloriapatricia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-29 10:19:54</t>
+          <t>2025-12-30 10:57:46</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788187866</t>
+          <t>788190176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gustavotellez</t>
+          <t>kei19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-29 10:44:48</t>
+          <t>2025-12-30 11:39:01</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788188313</t>
+          <t>788190335</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kerenrojasr</t>
+          <t>lizax567</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-29 14:33:34</t>
+          <t>2025-12-30 12:58:21</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788188826</t>
+          <t>788190542</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>huamani123</t>
+          <t>javier76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-29 19:23:07</t>
+          <t>2025-12-30 14:37:26</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788188931</t>
+          <t>788190551</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JeanBilletes</t>
+          <t>lobito123</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-29 21:33:02</t>
+          <t>2025-12-30 14:45:25</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788188961</t>
+          <t>788190854</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jean1201c</t>
+          <t>Tachaaa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/112.36</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,391 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-29 22:07:28</t>
+          <t>2025-12-30 17:45:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>788190911</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yessica</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2025-12-30 18:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>788190917</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Jhey214</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2025-12-30 18:22:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>788190926</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jeanpierre05</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2025-12-30 18:23:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>788190938</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Daisych</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2025-12-30 18:28:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>788190944</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DIEGOLABENITA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2025-12-30 18:31:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>788190947</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Carlosch</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2025-12-30 18:32:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>788190974</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>davor_ordi20</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2025-12-30 18:56:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>788191019</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wilmergalepa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2025-12-30 19:42:20</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788189876</t>
+          <t>788195090</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bettito1972</t>
+          <t>jorgitoquisperivas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-12-30 09:14:35</t>
+          <t>2026-01-02 08:27:00</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788190101</t>
+          <t>788195366</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gloriapatricia</t>
+          <t>ANTNT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/150.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-30 10:57:46</t>
+          <t>2026-01-02 10:18:43</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788190176</t>
+          <t>788195519</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kei19</t>
+          <t>Nlrioja</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-12-30 11:39:01</t>
+          <t>2026-01-02 10:59:52</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788190335</t>
+          <t>788195675</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lizax567</t>
+          <t>ANTUANPORTAL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-12-30 12:58:21</t>
+          <t>2026-01-02 12:06:51</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788190542</t>
+          <t>788195837</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>javier76</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-12-30 14:37:26</t>
+          <t>2026-01-02 13:24:14</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788190551</t>
+          <t>788195870</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lobito123</t>
+          <t>delicitatomi7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/400.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-12-30 14:45:25</t>
+          <t>2026-01-02 13:34:13</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788190854</t>
+          <t>788196092</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tachaaa</t>
+          <t>uber2005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-12-30 17:45:09</t>
+          <t>2026-01-02 15:25:58</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788190911</t>
+          <t>788196122</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yessica</t>
+          <t>villantoy29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-12-30 18:21:46</t>
+          <t>2026-01-02 15:49:59</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788190917</t>
+          <t>788196470</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jhey214</t>
+          <t>Puse</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-12-30 18:22:12</t>
+          <t>2026-01-02 19:29:07</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788190926</t>
+          <t>788196500</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jeanpierre05</t>
+          <t>BERAMENDI15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-12-30 18:23:06</t>
+          <t>2026-01-02 19:48:38</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788190938</t>
+          <t>788196668</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daisych</t>
+          <t>Pablo1417jham</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-12-30 18:28:29</t>
+          <t>2026-01-02 22:38:30</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788190944</t>
+          <t>788197097</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DIEGOLABENITA</t>
+          <t>Jesusp.18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-12-30 18:31:39</t>
+          <t>2026-01-03 06:43:59</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788190947</t>
+          <t>788197469</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carlosch</t>
+          <t>41665961</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/172.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-12-30 18:32:46</t>
+          <t>2026-01-03 09:14:13</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788190974</t>
+          <t>788197574</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>davor_ordi20</t>
+          <t>chaspita</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-12-30 18:56:51</t>
+          <t>2026-01-03 09:57:41</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788191019</t>
+          <t>788197805</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmergalepa</t>
+          <t>timana15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,679 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-12-30 19:42:20</t>
+          <t>2026-01-03 11:57:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>788197994</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>quispequispe10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-01-03 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>788198090</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>morecastro123</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-01-03 14:28:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>788198108</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AlexandreMeA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-01-03 14:39:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>788198255</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Faustino20</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-01-03 16:34:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>788198264</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>janrodavid05</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-01-03 16:43:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>788199365</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>axelcaritimari</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-01-04 08:45:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>788199470</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>orlin</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-01-04 09:35:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>788199539</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reyter</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-01-04 10:01:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>788199704</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>coral2107</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-01-04 11:07:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>788200079</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lucio1802</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-01-04 13:57:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>788200304</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>castillon26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-01-04 15:55:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>788200337</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ortizmartinez123</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-01-04 16:13:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>788200592</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>009049341</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S/7.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-01-04 19:39:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>788200778</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>svedra</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-01-04 23:02:32</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788201150</t>
+          <t>788202461</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jaquelin</t>
+          <t>luisdomza190390</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-01-05 07:59:01</t>
+          <t>2026-01-06 02:24:16</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788201705</t>
+          <t>788202980</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vmanu29</t>
+          <t>jeiver</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/400.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-01-05 12:52:35</t>
+          <t>2026-01-06 09:51:26</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788202068</t>
+          <t>788203007</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIOMAR94</t>
+          <t>Hyogita</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-01-05 17:03:12</t>
+          <t>2026-01-06 10:13:58</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788202359</t>
+          <t>788203022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estelita</t>
+          <t>JACOBO01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,343 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-05 22:06:13</t>
+          <t>2026-01-06 10:26:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>788203319</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ANNY26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-01-06 13:08:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>788203637</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ALAMO17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-01-06 16:15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>788203811</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jozito28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-01-06 18:24:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>788203949</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gilmar1996</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-01-06 19:55:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>788203955</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>peluchegugu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-01-06 20:04:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>788203958</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jherar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-01-06 20:05:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>788204126</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jdvill</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-01-06 22:34:57</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788202461</t>
+          <t>788206286</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>luisdomza190390</t>
+          <t>dinaq3749</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-01-06 02:24:16</t>
+          <t>2026-01-08 00:23:47</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788202980</t>
+          <t>788206892</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jeiver</t>
+          <t>sajami123</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-01-06 09:51:26</t>
+          <t>2026-01-08 09:25:29</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788203007</t>
+          <t>788207075</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hyogita</t>
+          <t>martinez123</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-01-06 10:13:58</t>
+          <t>2026-01-08 10:47:49</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788203022</t>
+          <t>788207288</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JACOBO01</t>
+          <t>arzola27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-06 10:26:27</t>
+          <t>2026-01-08 12:26:15</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788203319</t>
+          <t>788207360</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANNY26</t>
+          <t>JAlexisc10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-01-06 13:08:40</t>
+          <t>2026-01-08 12:57:23</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788203637</t>
+          <t>788207414</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALAMO17</t>
+          <t>JHONSURCO1995</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,247 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-01-06 16:15:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>788203811</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Jozito28</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-01-06 18:24:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>788203949</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>gilmar1996</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-01-06 19:55:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>788203955</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>peluchegugu</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-01-06 20:04:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>788203958</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jherar</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-01-06 20:05:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>788204126</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Jdvill</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>S/0.00</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ACP</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Habilitado</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-01-06 22:34:57</t>
+          <t>2026-01-08 13:20:32</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788206286</t>
+          <t>788215280</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dinaq3749</t>
+          <t>Hengel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-01-08 00:23:47</t>
+          <t>2026-01-13 09:01:53</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788206892</t>
+          <t>788215415</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sajami123</t>
+          <t>justin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-01-08 09:25:29</t>
+          <t>2026-01-13 10:09:24</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788207075</t>
+          <t>788215487</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>martinez123</t>
+          <t>Rodil</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-01-08 10:47:49</t>
+          <t>2026-01-13 10:45:05</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788207288</t>
+          <t>788215595</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>arzola27</t>
+          <t>60361659</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-08 12:26:15</t>
+          <t>2026-01-13 11:27:47</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788207360</t>
+          <t>788215718</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAlexisc10</t>
+          <t>wilsoncruz1992</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-01-08 12:57:23</t>
+          <t>2026-01-13 12:07:10</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788207414</t>
+          <t>788216312</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JHONSURCO1995</t>
+          <t>RAULZELL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,55 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-01-08 13:20:32</t>
+          <t>2026-01-13 16:53:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>788216615</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jorgelucs97</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-01-13 20:52:31</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788215280</t>
+          <t>788219399</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hengel</t>
+          <t>ericocastro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-01-13 09:01:53</t>
+          <t>2026-01-15 11:07:47</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788215415</t>
+          <t>788219432</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>justin</t>
+          <t>Ceferina123</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-01-13 10:09:24</t>
+          <t>2026-01-15 11:25:21</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788215487</t>
+          <t>788219444</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rodil</t>
+          <t>ELIEZER2010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-01-13 10:45:05</t>
+          <t>2026-01-15 11:32:35</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788215595</t>
+          <t>788219462</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60361659</t>
+          <t>Leo2002</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/833.40</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-13 11:27:47</t>
+          <t>2026-01-15 11:42:41</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788215718</t>
+          <t>788219924</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wilsoncruz1992</t>
+          <t>Edwinjuan76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-01-13 12:07:10</t>
+          <t>2026-01-15 16:42:23</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788216312</t>
+          <t>788219966</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAULZELL</t>
+          <t>jxi0201</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-01-13 16:53:31</t>
+          <t>2026-01-15 17:21:42</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788216615</t>
+          <t>788220056</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jorgelucs97</t>
+          <t>Understar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,151 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-01-13 20:52:31</t>
+          <t>2026-01-15 18:30:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>788220071</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>diegoxd</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-01-15 18:37:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>788220074</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>paolo031110</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-01-15 18:39:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>788220218</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Maritoliza</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-01-15 20:47:11</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788219399</t>
+          <t>788220959</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ericocastro</t>
+          <t>Yordisito1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/33.78</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-01-15 11:07:47</t>
+          <t>2026-01-16 10:05:07</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788219432</t>
+          <t>788221106</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ceferina123</t>
+          <t>ALEXPOCCO1996</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.24</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-01-15 11:25:21</t>
+          <t>2026-01-16 11:16:03</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788219444</t>
+          <t>788221226</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ELIEZER2010</t>
+          <t>Angisita10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/33.18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-01-15 11:32:35</t>
+          <t>2026-01-16 12:48:09</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788219462</t>
+          <t>788221310</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leo2002</t>
+          <t>yulino</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S/833.40</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-15 11:42:41</t>
+          <t>2026-01-16 13:39:25</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788219924</t>
+          <t>788221493</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Edwinjuan76</t>
+          <t>22216678</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/11.80</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-01-15 16:42:23</t>
+          <t>2026-01-16 15:36:03</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788219966</t>
+          <t>788221805</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jxi0201</t>
+          <t>argenis13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-01-15 17:21:42</t>
+          <t>2026-01-16 19:41:34</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788220056</t>
+          <t>788222735</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Understar</t>
+          <t>eltontello403</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-01-15 18:30:12</t>
+          <t>2026-01-17 11:11:36</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788220071</t>
+          <t>788222744</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>diegoxd</t>
+          <t>Khalef22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-01-15 18:37:11</t>
+          <t>2026-01-17 11:26:23</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788220074</t>
+          <t>788222876</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>paolo031110</t>
+          <t>jhony1997</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-01-15 18:39:58</t>
+          <t>2026-01-17 13:05:19</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788220218</t>
+          <t>788222930</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Maritoliza</t>
+          <t>mauricio29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,487 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-01-15 20:47:11</t>
+          <t>2026-01-17 13:36:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>788222987</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>julio1987</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-01-17 14:18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>788223089</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jeniferlala</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-01-17 15:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>788223191</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SALYNKEWIN1996</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-01-17 16:33:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>788223194</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>silvale</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-01-17 16:34:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>788223488</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Clotisita7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-01-17 21:45:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>788223944</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>elgabysueltala</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-01-18 07:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>788223962</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sifontesoswaldo09</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-01-18 07:36:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>788224475</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Carlitosalsa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S/0.12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-01-18 12:36:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>788224649</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>reymondscr</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S/5.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-01-18 14:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>788225039</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>millercoz3011</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-01-18 21:47:48</t>
         </is>
       </c>
     </row>

--- a/Archivos/Diario-ACPE.xlsx
+++ b/Archivos/Diario-ACPE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,12 +480,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>788220959</t>
+          <t>788225465</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yordisito1</t>
+          <t>Leandro18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S/33.78</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-01-16 10:05:07</t>
+          <t>2026-01-19 09:11:40</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>788221106</t>
+          <t>788225924</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALEXPOCCO1996</t>
+          <t>camir1416</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/0.12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-01-16 11:16:03</t>
+          <t>2026-01-19 14:38:51</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>788221226</t>
+          <t>788226017</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Angisita10</t>
+          <t>Ronicha97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S/33.18</t>
+          <t>S/0.03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-01-16 12:48:09</t>
+          <t>2026-01-19 15:31:23</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>788221310</t>
+          <t>788226050</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yulino</t>
+          <t>lucero.sosa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-01-16 13:39:25</t>
+          <t>2026-01-19 16:10:40</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>788221493</t>
+          <t>788226188</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22216678</t>
+          <t>eyauriscon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S/11.80</t>
+          <t>S/103.81</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-01-16 15:36:03</t>
+          <t>2026-01-19 18:03:14</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>788221805</t>
+          <t>788226263</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>argenis13</t>
+          <t>elpoyino</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/107.84</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-01-16 19:41:34</t>
+          <t>2026-01-19 19:26:35</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>788222735</t>
+          <t>788226275</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eltontello403</t>
+          <t>KarolJPR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/50.06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-01-17 11:11:36</t>
+          <t>2026-01-19 19:32:50</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>788222744</t>
+          <t>788226281</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Khalef22</t>
+          <t>Yorina</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-01-17 11:26:23</t>
+          <t>2026-01-19 19:35:12</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>788222876</t>
+          <t>788226368</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jhony1997</t>
+          <t>morter442</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/112.21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-01-17 13:05:19</t>
+          <t>2026-01-19 21:18:27</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>788222930</t>
+          <t>788226377</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mauricio29</t>
+          <t>robertjoshue</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-01-17 13:36:09</t>
+          <t>2026-01-19 21:25:52</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>788222987</t>
+          <t>788226401</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>julio1987</t>
+          <t>Evi152002</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S/0.00</t>
+          <t>S/100.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-01-17 14:18:49</t>
+          <t>2026-01-19 22:14:45</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>788223089</t>
+          <t>788226419</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jeniferlala</t>
+          <t>Juanjopr</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-01-17 15:14:37</t>
+          <t>2026-01-19 22:42:20</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>788223191</t>
+          <t>788226422</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SALYNKEWIN1996</t>
+          <t>Flaviojose</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-01-17 16:33:57</t>
+          <t>2026-01-19 22:43:39</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>788223194</t>
+          <t>788226434</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>silvale</t>
+          <t>Miledkrissty</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-01-17 16:34:28</t>
+          <t>2026-01-19 22:57:00</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>788223488</t>
+          <t>788226437</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clotisita7</t>
+          <t>Juanjopr99</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-01-17 21:45:58</t>
+          <t>2026-01-19 23:07:03</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>788223944</t>
+          <t>788227094</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>elgabysueltala</t>
+          <t>wilianlunacampana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-01-18 07:27:50</t>
+          <t>2026-01-20 10:41:04</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>788223962</t>
+          <t>788227235</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sifontesoswaldo09</t>
+          <t>BALAREZO7644</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-01-18 07:36:48</t>
+          <t>2026-01-20 11:57:23</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>788224475</t>
+          <t>788227277</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carlitosalsa</t>
+          <t>Yaqui35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S/0.12</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-01-18 12:36:34</t>
+          <t>2026-01-20 12:15:37</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>788224649</t>
+          <t>788227652</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>reymondscr</t>
+          <t>CHELITA24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S/5.00</t>
+          <t>S/0.00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-01-18 14:16:55</t>
+          <t>2026-01-20 15:02:54</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>788225039</t>
+          <t>788227850</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>millercoz3011</t>
+          <t>komboy2211</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1432,151 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-01-18 21:47:48</t>
+          <t>2026-01-20 17:43:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>788228024</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jeampieralexis03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-01-20 20:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>788228045</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Edilberto</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-01-20 20:34:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>788228063</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>wilmer1984</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>S/0.00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ACP</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Habilitado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-01-20 20:54:19</t>
         </is>
       </c>
     </row>
